--- a/docs/PRAP_Development_Plan_v2.48.xlsx
+++ b/docs/PRAP_Development_Plan_v2.48.xlsx
@@ -6794,7 +6794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7398,7 +7398,7 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-40, REQ-DSH-14: THREE LOOKUP COLUMNS, SO A TABLE SHOWING A FIGURE CAN SAY WHAT DECIDED ITS SIZE. Every figure in this application is standard FTE x period weight x (role factor / sharers) x person weight x month coverage, and three tables each showed one term of that and left the rest in another tab. (1) THE PERIODS TABLE now names the STANDARD MONTHLY FTE its period selects, beside the weight, and multiplies the two: 'Start-up 1.12 | 2.02 -&gt; 2.26 a month'. A row reading 'x1.12' said this study is an eighth heavier than usual and did not say heavier than WHAT - answerable only by leaving the tab and reading a 48-row matrix on General assumptions for one figure. (2) BOTH MONTHLY ESTIMATION PANELS name the PERIOD the month falls in and its weight, and (3) THE PERSON'S ALSO NAMES THE DIVISOR - how many people held that role that month. Those are the two usual explanations for a figure that is not the size somebody expected: the month moved into a heavier period, or a second holder arrived and halved the share. The project's panel deliberately does NOT carry the divisor: a project month is divided between several roles, each with its own count, so one number there would average things that do not compare. LOOKED UP, NEVER STORED. None of the three is a column of the sheet it sits beside, and the tests hold them to that - a standard copied onto a ProjectPeriod row would survive the standards being edited afterwards, which is the whole failure the lookup avoids. Read off the calculation's own lines, so a screen cannot name one period while the figure beside it came from another; calculate() now hands out periodAt for the one case the lines cannot answer, a manual project month with nobody assigned to it (V-32). A missing standard says 'none - V-19' rather than printing the 1.00 the calculation falls back to; that fallback is a degradation and showing it as a standard would hide exactly what V-19 reports. No calculation change and no figure moves. tools/test_lookup.py is new: a three-month fixture whose every figure is workable by hand, checking each column against the calculation's own line rather than against a plausible number.</t>
+          <t>R-41, REQ-DSH-14 EXTENDED: THE DERIVATION COLUMN NOW CARRIES THE WHOLE EXPRESSION, TERM BY TERM, rather than the period alone. Naming the period answered one of six inputs, and a reader who disagrees with an automatic figure needs to know WHICH of the six they disagree with. The project's month reads 'Before-Start-up (standard 2.02) × period weight (1.12) × month run (1.00) = 2.26'; a person's adds a second line, 'role factor (0.72) ÷ sharers (1) × person weight (0.25, no override) × coverage (1.00) = 18.3% of it → 0.41'. TWO HALVES, AND THE SPLIT IS THE CORRECTNESS OF IT. Since R-32 a person's figure is NOT the product of their own terms: those terms make a CLAIM, normalised against every other claim on the project-month to give a SHARE (REQ-CAL-19). The terms above multiply to 0.18 and the figure is 0.41. Written as one product the cell would assert an arithmetic the application does not do and would be wrong by whatever the other claims came to - so the demand is closed off with its own '=', and the person's terms end in a PERCENTAGE of it. AN OVERRIDE IS ONE TERM WITH TWO SOURCES, not two multiplied terms. A PersonPeriodWeight window REPLACES person_weight for the months it covers (REQ-PSN-05); the request asked for it as its own factor, which would have read as a multiplication that does not happen, so the cell names both values and says which was used: 'weight override (0.50, replacing person weight 1.00)'. EVERY FALLBACK NOW SAYS IT IS ONE and names its rule - V-19 for a missing standard, V-23 for a missing role factor, V-12 for a month in no period. A bare 1.00 is indistinguishable from a standard that really is 1.00, which is the whole reason those rules exist. Absorbed cover is named too, with the roles it came from (REQ-CAL-16). The sharer count KEEPS its own short column: the derivation is a sentence, and a sentence cannot be sorted or filtered, while '2 share this role' can. The cost of the change is that the derivation column is no longer a useful filter - it is now nearly unique per row - which is why the short column stays. No calculation change and no figure moves.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -7450,19 +7450,19 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>R-39, PROJECT AND PERSON FIGURES KEPT CONSISTENT, AND SAID TO BE. (1) THE FIRST REQUEST WAS ALREADY THE BEHAVIOUR, which is worth recording rather than quietly re-implementing: a manual PROJECT month has always realigned every person on it, including anyone whose own figure is manual, because applyManual applies the assignment level first and then scales the whole group to the project's stated total. Verified: project set to 10.00 with a person stating 99.00 gives the person 9.97 and the month 10.00. The project figure is the mother figure and wins. (2) WHAT WAS MISSING IS THAT NOTHING SAID SO. The sheet held 99.00, the chart showed 9.97, and nothing connected them. Now V-33 reports it; the Monthly estimation panel carries a table of stated against actually-given against the project's month; the cell is marked; and editing such a figure SOFT-STOPS at the cell - naming both numbers, offering Keep what I typed or Put it back. It never refuses: both numbers were typed deliberately and which is wrong is not the application's judgement. The finding reaches the findings report and the archived change log, so it is on the record either way. (3) automatic_fte and difference in the Monthly estimation tables were the last four-place figures on screen and are now two, like everything else (REQ-CAL-20). A stated 2.41 beside an automatic 2.4120 read as a discrepancy the user had caused rather than as four decimals nothing else uses. One defect found by testing the undo rather than by reading it: rebuild() makes fresh row objects, so the row reference captured before it was orphaned and 'Put it back' silently did nothing. It re-finds the row by number now.</t>
+          <t>R-40, REQ-DSH-14: THREE LOOKUP COLUMNS, SO A TABLE SHOWING A FIGURE CAN SAY WHAT DECIDED ITS SIZE. Every figure in this application is standard FTE x period weight x (role factor / sharers) x person weight x month coverage, and three tables each showed one term of that and left the rest in another tab. (1) THE PERIODS TABLE now names the STANDARD MONTHLY FTE its period selects, beside the weight, and multiplies the two: 'Start-up 1.12 | 2.02 -&gt; 2.26 a month'. A row reading 'x1.12' said this study is an eighth heavier than usual and did not say heavier than WHAT - answerable only by leaving the tab and reading a 48-row matrix on General assumptions for one figure. (2) BOTH MONTHLY ESTIMATION PANELS name the PERIOD the month falls in and its weight, and (3) THE PERSON'S ALSO NAMES THE DIVISOR - how many people held that role that month. Those are the two usual explanations for a figure that is not the size somebody expected: the month moved into a heavier period, or a second holder arrived and halved the share. The project's panel deliberately does NOT carry the divisor: a project month is divided between several roles, each with its own count, so one number there would average things that do not compare. LOOKED UP, NEVER STORED. None of the three is a column of the sheet it sits beside, and the tests hold them to that - a standard copied onto a ProjectPeriod row would survive the standards being edited afterwards, which is the whole failure the lookup avoids. Read off the calculation's own lines, so a screen cannot name one period while the figure beside it came from another; calculate() now hands out periodAt for the one case the lines cannot answer, a manual project month with nobody assigned to it (V-32). A missing standard says 'none - V-19' rather than printing the 1.00 the calculation falls back to; that fallback is a degradation and showing it as a standard would hide exactly what V-19 reports. No calculation change and no figure moves. tools/test_lookup.py is new: a three-month fixture whose every figure is workable by hand, checking each column against the calculation's own line rather than against a plausible number.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.48</t>
+          <t>Issued for review</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -7482,19 +7482,19 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>R-38, THREE REQUESTS. (1) THE IN-APP EXPORT OF THE CHANGE LOG IS REMOVED. The archive is written at every save, so a button handing over the same record afterwards was a second answer to one question and always the staler of the two. The menu items, the date range, the CSV download and the code behind them are gone rather than hidden. (2) THE ARCHIVE IS ONE FOLDER FOR THE INSTALLATION, beside users/ rather than inside any one person's copy of it - the layout PRAP_DATA and the shared-drive deployment already assume (NR-DEP-15). A log split per person answers 'what did I do' and not 'what happened to this plan', and on a shared deployment only the second question is worth asking; every row already names who made the change. NOT YET BUILT, and stated so the gap is not mistaken for done: a CENTRAL SERVER needs network binding, real authentication and sessions, per-user authorisation and concurrent-write handling. The shell today binds to 127.0.0.1 and refuses non-loopback Host headers BY DESIGN - that refusal is what makes an open socket on a company laptop defensible - and 'login' is the Windows account name, a label rather than an authentication. Replacing that is a security-sensitive piece of work to be specified before it is started. (3) REQ-CAL-20, THE DECIMAL RULE - see the requirement for the whole of it. EVERY FIGURE IN EVERY PLAN MOVES slightly: the 62-project fixture goes 4,333.46 to 4,333.77 FTE-months and the 10x10 fixture 713.94 to 713.78, which is the rounding and nothing else. Checked on the 62-project fixture: all 7,001 lines are whole hundredths, all 1,629 project-months have their lines summing to the month with nothing left over, and all 1,557 automatic months still equal standard x weight x month_run to the hundredth. All four implementations agree line for line - 7,001 lines and 1,629 project-months identical between the browser and prap_io.</t>
+          <t>R-39, PROJECT AND PERSON FIGURES KEPT CONSISTENT, AND SAID TO BE. (1) THE FIRST REQUEST WAS ALREADY THE BEHAVIOUR, which is worth recording rather than quietly re-implementing: a manual PROJECT month has always realigned every person on it, including anyone whose own figure is manual, because applyManual applies the assignment level first and then scales the whole group to the project's stated total. Verified: project set to 10.00 with a person stating 99.00 gives the person 9.97 and the month 10.00. The project figure is the mother figure and wins. (2) WHAT WAS MISSING IS THAT NOTHING SAID SO. The sheet held 99.00, the chart showed 9.97, and nothing connected them. Now V-33 reports it; the Monthly estimation panel carries a table of stated against actually-given against the project's month; the cell is marked; and editing such a figure SOFT-STOPS at the cell - naming both numbers, offering Keep what I typed or Put it back. It never refuses: both numbers were typed deliberately and which is wrong is not the application's judgement. The finding reaches the findings report and the archived change log, so it is on the record either way. (3) automatic_fte and difference in the Monthly estimation tables were the last four-place figures on screen and are now two, like everything else (REQ-CAL-20). A stated 2.41 beside an automatic 2.4120 read as a discrepancy the user had caused rather than as four decimals nothing else uses. One defect found by testing the undo rather than by reading it: rebuild() makes fresh row objects, so the row reference captured before it was orphaned and 'Put it back' silently did nothing. It re-finds the row by number now.</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.47</t>
+          <t>Superseded by v2.48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -7514,24 +7514,24 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>R-37, THE POP-UPS NAME THE PROJECT PERIOD. Every figure in this application is standard FTE x PERIOD WEIGHT x the month the project ran, so the period is the row of the plan that decided the size of whatever is being hovered over - and it was the one thing the pop-ups did not say. A reader who thought a month looked heavy had to leave the chart, find the project and read its periods to learn the month was mid-Conduct. All four charts named in the request now carry it: both Overall stacks, and Utilisation on each source-data tab. The WEIGHT goes with the name, because the two are one fact - which row applied, and what it did to the figure. READ FROM THE CALCULATION, not looked up again. calculate() already stamped period_name on every line, so it now also returns projPeriod (project|month -&gt; name and weight) built from those same lines, exactly as projMonth and persMonth are. A second lookup could name one period while the number beside it came from another; this cannot. Checked on 154 project-months against S.calc.lines, all matching, and the check fails if the tooltip line is removed. WHERE ONE BAND SPANS SEVERAL PROJECTS - the person stack and the person Utilisation chart - the period is tagged against EACH PROJECT rather than against the band, because a person's month is made of projects that need not be in the same period as each other; the delivered fixture has a person in Conduct (final) on one project and Conduct (interim) on another in the same month. A month belonging to no period says so and names V-12, rather than leaving a blank that reads as a defect in the chart. No figure moves.</t>
+          <t>R-38, THREE REQUESTS. (1) THE IN-APP EXPORT OF THE CHANGE LOG IS REMOVED. The archive is written at every save, so a button handing over the same record afterwards was a second answer to one question and always the staler of the two. The menu items, the date range, the CSV download and the code behind them are gone rather than hidden. (2) THE ARCHIVE IS ONE FOLDER FOR THE INSTALLATION, beside users/ rather than inside any one person's copy of it - the layout PRAP_DATA and the shared-drive deployment already assume (NR-DEP-15). A log split per person answers 'what did I do' and not 'what happened to this plan', and on a shared deployment only the second question is worth asking; every row already names who made the change. NOT YET BUILT, and stated so the gap is not mistaken for done: a CENTRAL SERVER needs network binding, real authentication and sessions, per-user authorisation and concurrent-write handling. The shell today binds to 127.0.0.1 and refuses non-loopback Host headers BY DESIGN - that refusal is what makes an open socket on a company laptop defensible - and 'login' is the Windows account name, a label rather than an authentication. Replacing that is a security-sensitive piece of work to be specified before it is started. (3) REQ-CAL-20, THE DECIMAL RULE - see the requirement for the whole of it. EVERY FIGURE IN EVERY PLAN MOVES slightly: the 62-project fixture goes 4,333.46 to 4,333.77 FTE-months and the 10x10 fixture 713.94 to 713.78, which is the rounding and nothing else. Checked on the 62-project fixture: all 7,001 lines are whole hundredths, all 1,629 project-months have their lines summing to the month with nothing left over, and all 1,557 automatic months still equal standard x weight x month_run to the hundredth. All four implementations agree line for line - 7,001 lines and 1,629 project-months identical between the browser and prap_io.</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.46</t>
+          <t>Superseded by v2.47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -7546,19 +7546,19 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>R-36, A CHANGE LOG AND COLUMN FILTERS. Two requests; no figure moves for either. (1) THE CHANGE LOG. Every saved change is recorded - the time in UTC, who, which RECORD (its natural key, not its spreadsheet row: inserting a row renumbers everything under it and PRJ-004 does not move), which column, and the value before and after - together with the errors and warnings standing at each save and which of them the user was asked about and chose to keep. It is NOT S.pending: that is emptied at every save because its job is 'what is not saved yet', and this is only ever appended to, with a save being what WRITES it rather than what clears it. Asked for as an in-app tab first and then narrowed by the requester to 'in memory while the session runs, archived to a local folder on Save, CSV is enough' - so there is no tab and no schema change. THE DESKTOP SHELL archives it: an `audit` folder beside the workspaces, one CSV a month, header written when the file is created and rows APPENDED at every save. THE BROWSER CANNOT do that - a file:// page has no folder and cannot append to one - so it holds the record for the session and hands it over from Export, narrowed by a date range, which was the other half of the request. A failed archive never fails a save: the entries stay and the next save carries them too. WHO: the desktop shell takes the Windows account it already signed in with; the browser asks once, in the EDIT BAR rather than in a dialog - a modal blocks the cell being typed into, and a floating card sits on top of the table. Both were built and both were wrong before the bar was tried. (2) COLUMN FILTERS on the six tables named: Projects, Monthly estimation (both tabs), People, Standard period FTE for project types and Role factors. A spreadsheet's filter - tick the values to keep, different columns narrow together, and the values offered are what the OTHER columns leave reachable. It narrows the TABLE and not the plan: the charts and totals above are unchanged, because a row hidden here is still in the plan, and the horizon-and-filters bar remains the one control that changes what the figures mean. Two new suites, test_audit.py and test_colfilter.py; the storage seam budget in test_layers.py re-baselined 150 -&gt; 220 and the reason recorded, since the seam legitimately gained a third responsibility.</t>
+          <t>R-37, THE POP-UPS NAME THE PROJECT PERIOD. Every figure in this application is standard FTE x PERIOD WEIGHT x the month the project ran, so the period is the row of the plan that decided the size of whatever is being hovered over - and it was the one thing the pop-ups did not say. A reader who thought a month looked heavy had to leave the chart, find the project and read its periods to learn the month was mid-Conduct. All four charts named in the request now carry it: both Overall stacks, and Utilisation on each source-data tab. The WEIGHT goes with the name, because the two are one fact - which row applied, and what it did to the figure. READ FROM THE CALCULATION, not looked up again. calculate() already stamped period_name on every line, so it now also returns projPeriod (project|month -&gt; name and weight) built from those same lines, exactly as projMonth and persMonth are. A second lookup could name one period while the number beside it came from another; this cannot. Checked on 154 project-months against S.calc.lines, all matching, and the check fails if the tooltip line is removed. WHERE ONE BAND SPANS SEVERAL PROJECTS - the person stack and the person Utilisation chart - the period is tagged against EACH PROJECT rather than against the band, because a person's month is made of projects that need not be in the same period as each other; the delivered fixture has a person in Conduct (final) on one project and Conduct (interim) on another in the same month. A month belonging to no period says so and names V-12, rather than leaving a blank that reads as a defect in the chart. No figure moves.</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.45</t>
+          <t>Superseded by v2.46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -7578,19 +7578,19 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>R-35, TWO FAULTS IN THE DATE PICKER, both reported from the field and both reproduced before being touched. (1) THE MONTH ARROWS MOVED ONE MONTH AND NO FURTHER. step() re-read the cell and snapped the grid back to the cell's own month before stepping, so a cell holding 2026-09-01 went to August and stayed at August however many times the arrow was pressed - a date several months away could not be reached by navigating at all. It had a workaround that did not work: blank the cell, render, put the text back, which step() then defeated by re-reading before it rendered. The grid now knows WHO IS STEERING - the cell while it is being opened or typed into, the user while they are working the arrows - and the cell keeps its text throughout. (2) 'TODAY' WROTE THE DATE IN GREENWICH, not on the user's clock. ymd() is toISOString(), which is right for every other date in the application because those are built with Date.UTC(); `new Date()` is an instant, and putting an instant through a UTC formatter asks what day it is in London. In Seoul before 09:00 that is yesterday; in Los Angeles after 17:00 it is tomorrow. The local getters now read the date off the user's own calendar and Date.UTC puts it back into the form the rest of the application stores. The same figure highlights today in the grid and opens an empty cell on the right month. NO CALCULATION CHANGES. test_ui.py gains both: five clicks must move five months (the old test stepped ONCE, which is why this passed for so long - one step did work), and Today is checked in three time zones on a pinned clock, because CI keeps UTC and in UTC the wrong answer and the right one are the same answer. Both verified to fail against the old code.</t>
+          <t>R-36, A CHANGE LOG AND COLUMN FILTERS. Two requests; no figure moves for either. (1) THE CHANGE LOG. Every saved change is recorded - the time in UTC, who, which RECORD (its natural key, not its spreadsheet row: inserting a row renumbers everything under it and PRJ-004 does not move), which column, and the value before and after - together with the errors and warnings standing at each save and which of them the user was asked about and chose to keep. It is NOT S.pending: that is emptied at every save because its job is 'what is not saved yet', and this is only ever appended to, with a save being what WRITES it rather than what clears it. Asked for as an in-app tab first and then narrowed by the requester to 'in memory while the session runs, archived to a local folder on Save, CSV is enough' - so there is no tab and no schema change. THE DESKTOP SHELL archives it: an `audit` folder beside the workspaces, one CSV a month, header written when the file is created and rows APPENDED at every save. THE BROWSER CANNOT do that - a file:// page has no folder and cannot append to one - so it holds the record for the session and hands it over from Export, narrowed by a date range, which was the other half of the request. A failed archive never fails a save: the entries stay and the next save carries them too. WHO: the desktop shell takes the Windows account it already signed in with; the browser asks once, in the EDIT BAR rather than in a dialog - a modal blocks the cell being typed into, and a floating card sits on top of the table. Both were built and both were wrong before the bar was tried. (2) COLUMN FILTERS on the six tables named: Projects, Monthly estimation (both tabs), People, Standard period FTE for project types and Role factors. A spreadsheet's filter - tick the values to keep, different columns narrow together, and the values offered are what the OTHER columns leave reachable. It narrows the TABLE and not the plan: the charts and totals above are unchanged, because a row hidden here is still in the plan, and the horizon-and-filters bar remains the one control that changes what the figures mean. Two new suites, test_audit.py and test_colfilter.py; the storage seam budget in test_layers.py re-baselined 150 -&gt; 220 and the reason recorded, since the seam legitimately gained a third responsibility.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.44</t>
+          <t>Superseded by v2.45</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -7610,19 +7610,19 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>R-34, THE PROJECT DEMAND CHART SAYS WHAT ITS MONTH CAME TO. 'Monthly demand by person' ended its pop-up with a rule and the month's total across everyone in view, and gave each band its share of that month; 'Monthly demand by project' gave neither, only the band's own figure. A band read on its own cannot say whether the month came to five FTE or to fifty, which is the question a stacked chart exists to answer - so the reader had to leave the chart and find the Overall table to interpret what they were hovering over. Both are added, worded to match the person chart. The total is summed over every project IN VIEW rather than over the bands actually drawn, for the same reason the person chart sums over every person in view: so the two pop-ups report the SAME figure for a given month, which is what the panel caption already claims about these two charts. Checked on the 10x10 fixture - 24 months, every one identical between the two, and the per-band shares summing to 100% (+/-1, rounding to a whole percent) in all 24. NO FIGURE CHANGES: the total is the sum the chart was already drawing. test_charts.py gains two checks. It already compared the two charts as DRAWN, in pixel heights; these compare what they SAY, which is what a reader acts on - that every band states a month total, and that the total it states is the one the person chart states for that month. Both were verified to fail with the line removed from the build.</t>
+          <t>R-35, TWO FAULTS IN THE DATE PICKER, both reported from the field and both reproduced before being touched. (1) THE MONTH ARROWS MOVED ONE MONTH AND NO FURTHER. step() re-read the cell and snapped the grid back to the cell's own month before stepping, so a cell holding 2026-09-01 went to August and stayed at August however many times the arrow was pressed - a date several months away could not be reached by navigating at all. It had a workaround that did not work: blank the cell, render, put the text back, which step() then defeated by re-reading before it rendered. The grid now knows WHO IS STEERING - the cell while it is being opened or typed into, the user while they are working the arrows - and the cell keeps its text throughout. (2) 'TODAY' WROTE THE DATE IN GREENWICH, not on the user's clock. ymd() is toISOString(), which is right for every other date in the application because those are built with Date.UTC(); `new Date()` is an instant, and putting an instant through a UTC formatter asks what day it is in London. In Seoul before 09:00 that is yesterday; in Los Angeles after 17:00 it is tomorrow. The local getters now read the date off the user's own calendar and Date.UTC puts it back into the form the rest of the application stores. The same figure highlights today in the grid and opens an empty cell on the right month. NO CALCULATION CHANGES. test_ui.py gains both: five clicks must move five months (the old test stepped ONCE, which is why this passed for so long - one step did work), and Today is checked in three time zones on a pinned clock, because CI keeps UTC and in UTC the wrong answer and the right one are the same answer. Both verified to fail against the old code.</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.43</t>
+          <t>Superseded by v2.44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -7642,24 +7642,24 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>R-33, WHAT THE STANDARDS SHEET IS CALLED, and the notes that describe the calculation. Three things the reviewer reported after using v2.40, none of them arithmetic - every figure in this revision is unchanged, checked at 4,333.46 FTE-months on the 62-project fixture before and after. (1) SHEET RENAMED PeriodWeightStandard -&gt; PeriodFTEStandard, and the panel over it from 'Standard period weights' to 'Standard period FTE for project types'. Schema 10 renamed the COLUMN to standard_fte when it became clear the sheet holds a magnitude in FTE rather than a multiplier; the sheet and the panel went on saying 'weight', which is the reading that made the standards look ignorable in the first place - R-32 exists because of it. Source schema version steps 10 to 11. A schema 10 workbook still opens: the old sheet name is translated on the way in and the reader is told once, exactly as a renamed column is. (2) THE CALCULATION NOTES on the monthly-estimation panels still described the pre-R-32 formula - four factors multiplied together - which has not been how a figure is arrived at since v2.40. They now state it as it is, and separately for the two levels, because under R-32 the two genuinely differ: a PROJECT month is standard FTE x period weight x the part of the month the project ran, and an ASSIGNMENT month is that month divided by share, the share being (role factor / sharers) x person weight x coverage against everyone else's. Same correction to the automatic_fte and ProjectPeriod.weight column help and to the switch-back dialog. (3) THE WINDOW CHROME OVERLAPPED THE PAGE in the Python shell. Its menu bar and status strip are sticky at the top of the window and the page's own sticky band - the edit bar and the four tabs - pinned itself to the same place with a lower z-index, so scrolling slid the tabs and the Save button underneath the File menu. The band now sits below the chrome, at the chrome's MEASURED height: both bars wrap, so a constant would have been wrong exactly when it mattered.</t>
+          <t>R-34, THE PROJECT DEMAND CHART SAYS WHAT ITS MONTH CAME TO. 'Monthly demand by person' ended its pop-up with a rule and the month's total across everyone in view, and gave each band its share of that month; 'Monthly demand by project' gave neither, only the band's own figure. A band read on its own cannot say whether the month came to five FTE or to fifty, which is the question a stacked chart exists to answer - so the reader had to leave the chart and find the Overall table to interpret what they were hovering over. Both are added, worded to match the person chart. The total is summed over every project IN VIEW rather than over the bands actually drawn, for the same reason the person chart sums over every person in view: so the two pop-ups report the SAME figure for a given month, which is what the panel caption already claims about these two charts. Checked on the 10x10 fixture - 24 months, every one identical between the two, and the per-band shares summing to 100% (+/-1, rounding to a whole percent) in all 24. NO FIGURE CHANGES: the total is the sum the chart was already drawing. test_charts.py gains two checks. It already compared the two charts as DRAWN, in pixel heights; these compare what they SAY, which is what a reader acts on - that every band states a month total, and that the total it states is the one the person chart states for that month. Both were verified to fail with the line removed from the build.</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Issued for review</t>
+          <t>Superseded by v2.43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>R-31, REQ-CAL-19, SCHEMA 10: THE STANDARD IS WHERE A FIGURE GETS ITS SIZE, and until now it reached no figure at all. PeriodWeightStandard seeded a derived period's weight and fed V-19, and that was the whole of it: every number the application produced came from ProjectPeriod.weight times the role factors, which is a relative SHAPE with no magnitude behind it. Reported by the reviewer. Two things were wrong and the naming was most of the cause. The column was called `weight`, which reads like something to multiply by, so the calculation multiplied by the PROJECT's weight and never asked the standards sheet anything; and the delivered data seeded the project weight FROM the standard, so the two columns held the same number twice and reading both would have squared it. The column is now `standard_fte` and holds the month's DEMAND in FTE - 4.02 against NewDrug CT Phase 3 Start-up means that period takes about four full-time people a month. The formula becomes standard_fte x period weight x role_share x person weight x month coverage, where role_share is this role's effective factor divided by the people holding it, over the sum of the effective factors of the roles ACTUALLY STAFFED. Three consequences, each a decision the reviewer took: the shares add to one, so a fully committed project-month IS standard x period weight however many roles are on it; an unstaffed role's work lands on the others rather than making the project cheaper, which is REQ-CAL-16 arriving by construction (absorbed_by still decides WHERE it lands); and person_weight scales that person's share, so a part-time commitment leaves the project SHORT of its standard, which is the gap worth seeing. A missing standard falls back to 1.00 and V-19 reports it - deliberately the old behaviour, so an incomplete standards sheet degrades to figures its author recognises rather than to zero. stdWeight now nulls the phase for a non-clinical type exactly as stdFactor does; that cost nothing while the figure only seeded a period and is the difference between a real answer and 1.00 now. The delivered defaults are re-authored throughout: the standards carry FTE magnitudes, ProjectPeriod.weight becomes an adjustment around 1.00, and 'Others' projects gain the standards they never had. A schema 9 file still opens - the column is renamed on the way in. NOTE FOR THE REVIEWER: with real magnitudes the delivered 62-project / 20-person example is resourced at 17% of its own standard, which is arithmetic rather than a defect - 62 concurrent trials at these standards need about 59 people. The fixture keeps the size that was requested; the staffing assumptions are a data decision.</t>
+          <t>R-33, WHAT THE STANDARDS SHEET IS CALLED, and the notes that describe the calculation. Three things the reviewer reported after using v2.40, none of them arithmetic - every figure in this revision is unchanged, checked at 4,333.46 FTE-months on the 62-project fixture before and after. (1) SHEET RENAMED PeriodWeightStandard -&gt; PeriodFTEStandard, and the panel over it from 'Standard period weights' to 'Standard period FTE for project types'. Schema 10 renamed the COLUMN to standard_fte when it became clear the sheet holds a magnitude in FTE rather than a multiplier; the sheet and the panel went on saying 'weight', which is the reading that made the standards look ignorable in the first place - R-32 exists because of it. Source schema version steps 10 to 11. A schema 10 workbook still opens: the old sheet name is translated on the way in and the reader is told once, exactly as a renamed column is. (2) THE CALCULATION NOTES on the monthly-estimation panels still described the pre-R-32 formula - four factors multiplied together - which has not been how a figure is arrived at since v2.40. They now state it as it is, and separately for the two levels, because under R-32 the two genuinely differ: a PROJECT month is standard FTE x period weight x the part of the month the project ran, and an ASSIGNMENT month is that month divided by share, the share being (role factor / sharers) x person weight x coverage against everyone else's. Same correction to the automatic_fte and ProjectPeriod.weight column help and to the switch-back dialog. (3) THE WINDOW CHROME OVERLAPPED THE PAGE in the Python shell. Its menu bar and status strip are sticky at the top of the window and the page's own sticky band - the edit bar and the four tabs - pinned itself to the same place with a lower z-index, so scrolling slid the tabs and the Save button underneath the File menu. The band now sits below the chrome, at the chrome's MEASURED height: both bars wrap, so a constant would have been wrong exactly when it mattered.</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -7686,12 +7686,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>R-30, REQ-CAL-18, SCHEMA 9: A FIGURE CAN BE STATED INSTEAD OF CALCULATED. Until now every monthly FTE came from the assumptions, and on a project two years in that is often the worse of the two available answers - the manager knows what the rest of it takes, and a standard period weight multiplied by a standard role factor does not. Project and Assignment each gain estimation_type ('automatic' or 'manual'), and a new sheet MonthlyEstimate carries the stated figures, keyed on (scope, ref_id, month) so one sheet serves both levels. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution and replaces the multiplication outright; a PROJECT figure is the whole month, and the people on it are SCALED so they still add up to it - chosen over the alternatives because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one real guarantee. The scaling factor is recorded on every line, so a person whose figure moved without anything of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies EVERY month across from the figures currently on screen - to TWO DECIMAL PLACES, because a stated figure is one somebody reads and edits and 0.01 FTE is already 1.6 hours, so a month can move by up to 0.005 FTE at the moment of switching - so nothing jumps, and switching back discards the lot. That was chosen over per-month marking deliberately - once a figure has been edited, 'which months are still automatic' has no useful answer, because those would still move under a plan somebody has signed off whenever an assumption changed. What the user takes on in exchange is responsibility for all of them, and the confirmation says so in those words. EVERY CHANGE OF CALCULATION WAY IS CONFIRMED, in both directions, and typing 'manual' into the cell opens the same dialog rather than setting the flag - the flag without the copy would count every month as 0.00, which is the one change in the application that could silently zero a figure. V-31 reports a manual thing with a month carrying no figure; V-32 a project figure in a month nobody is assigned to, which cannot be shared out and is therefore NOT applied. Both are raised from the calculation, like V-23, because they are things that happened to a number. The stated figures round-trip through the source export, and the results export gains four columns - estimation, automatic_fte, project_manual_total, project_scale - so a reader can see which rows were stated, at which level, and what the assumptions would have said instead. Nothing moves on a file that uses none of it: test_app.py's four-way comparison agrees on all 1,227 and 441 person-months, and both dummy sets now carry a manual project and a manual assignment so the rule is under that comparison rather than in one unit test.</t>
+          <t>R-31, REQ-CAL-19, SCHEMA 10: THE STANDARD IS WHERE A FIGURE GETS ITS SIZE, and until now it reached no figure at all. PeriodWeightStandard seeded a derived period's weight and fed V-19, and that was the whole of it: every number the application produced came from ProjectPeriod.weight times the role factors, which is a relative SHAPE with no magnitude behind it. Reported by the reviewer. Two things were wrong and the naming was most of the cause. The column was called `weight`, which reads like something to multiply by, so the calculation multiplied by the PROJECT's weight and never asked the standards sheet anything; and the delivered data seeded the project weight FROM the standard, so the two columns held the same number twice and reading both would have squared it. The column is now `standard_fte` and holds the month's DEMAND in FTE - 4.02 against NewDrug CT Phase 3 Start-up means that period takes about four full-time people a month. The formula becomes standard_fte x period weight x role_share x person weight x month coverage, where role_share is this role's effective factor divided by the people holding it, over the sum of the effective factors of the roles ACTUALLY STAFFED. Three consequences, each a decision the reviewer took: the shares add to one, so a fully committed project-month IS standard x period weight however many roles are on it; an unstaffed role's work lands on the others rather than making the project cheaper, which is REQ-CAL-16 arriving by construction (absorbed_by still decides WHERE it lands); and person_weight scales that person's share, so a part-time commitment leaves the project SHORT of its standard, which is the gap worth seeing. A missing standard falls back to 1.00 and V-19 reports it - deliberately the old behaviour, so an incomplete standards sheet degrades to figures its author recognises rather than to zero. stdWeight now nulls the phase for a non-clinical type exactly as stdFactor does; that cost nothing while the figure only seeded a period and is the difference between a real answer and 1.00 now. The delivered defaults are re-authored throughout: the standards carry FTE magnitudes, ProjectPeriod.weight becomes an adjustment around 1.00, and 'Others' projects gain the standards they never had. A schema 9 file still opens - the column is renamed on the way in. NOTE FOR THE REVIEWER: with real magnitudes the delivered 62-project / 20-person example is resourced at 17% of its own standard, which is arithmetic rather than a defect - 62 concurrent trials at these standards need about 59 people. The fixture keeps the size that was requested; the staffing assumptions are a data decision.</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -7718,12 +7718,12 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>R-29, REQ-OUT-06: THE APPLICATION EXPORTS ITS ANSWERS AS WELL AS ITS QUESTIONS. Until now Export meant one thing - the plan, so it could come back - and there was no way to get the monthly figures out for a report, a spreadsheet or somebody else's model short of reading them off the screen. The export control is now a MENU with the choice on it: the plan as .xlsx or as the interchange file, both of which round-trip, or the CALCULATED MONTHLY FTE, which deliberately does not. Each item says which it is, so the choice can be made without trying it. The results workbook carries seven sheets: a ReadMe that states it cannot be imported and gives the formula; Summary, the Overall tab's tiles as figures; ProjectMonth and PersonMonth, one row each per month; DETAIL, one row per assignment per month carrying every term of the multiplication that produced it - period weight, the role factor before and after absorption, the number of sharers, the person weight and which row it came from, the month coverage; Flags, the over-allocated months and under-allocated runs; and Assumptions, the settings in force, marked for whether each one changed a figure or only its display. Two properties are held by test_results.py rather than asserted: every project-month and person-month is EXACTLY the sum of its Detail rows and all four totals in the file are the same number - the monthly sheets are summed FROM the detail rather than from the engine, so a reader who adds the column gets the total - and every Detail row reconciles to its own four numbers. The file covers what was ON SCREEN, horizon and filters included, and the ReadMe names them, so a file that has left the building can still say what it does and does not cover. The calculation now records each term as it works it out (calculate() returns `lines`), because an explanation assembled afterwards from the sheets could drift from the figure it claims to explain.</t>
+          <t>R-30, REQ-CAL-18, SCHEMA 9: A FIGURE CAN BE STATED INSTEAD OF CALCULATED. Until now every monthly FTE came from the assumptions, and on a project two years in that is often the worse of the two available answers - the manager knows what the rest of it takes, and a standard period weight multiplied by a standard role factor does not. Project and Assignment each gain estimation_type ('automatic' or 'manual'), and a new sheet MonthlyEstimate carries the stated figures, keyed on (scope, ref_id, month) so one sheet serves both levels. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution and replaces the multiplication outright; a PROJECT figure is the whole month, and the people on it are SCALED so they still add up to it - chosen over the alternatives because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one real guarantee. The scaling factor is recorded on every line, so a person whose figure moved without anything of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies EVERY month across from the figures currently on screen - to TWO DECIMAL PLACES, because a stated figure is one somebody reads and edits and 0.01 FTE is already 1.6 hours, so a month can move by up to 0.005 FTE at the moment of switching - so nothing jumps, and switching back discards the lot. That was chosen over per-month marking deliberately - once a figure has been edited, 'which months are still automatic' has no useful answer, because those would still move under a plan somebody has signed off whenever an assumption changed. What the user takes on in exchange is responsibility for all of them, and the confirmation says so in those words. EVERY CHANGE OF CALCULATION WAY IS CONFIRMED, in both directions, and typing 'manual' into the cell opens the same dialog rather than setting the flag - the flag without the copy would count every month as 0.00, which is the one change in the application that could silently zero a figure. V-31 reports a manual thing with a month carrying no figure; V-32 a project figure in a month nobody is assigned to, which cannot be shared out and is therefore NOT applied. Both are raised from the calculation, like V-23, because they are things that happened to a number. The stated figures round-trip through the source export, and the results export gains four columns - estimation, automatic_fte, project_manual_total, project_scale - so a reader can see which rows were stated, at which level, and what the assumptions would have said instead. Nothing moves on a file that uses none of it: test_app.py's four-way comparison agrees on all 1,227 and 441 person-months, and both dummy sets now carry a manual project and a manual assignment so the rule is under that comparison rather than in one unit test.</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -7750,7 +7750,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>R-28, REQ-IMP-14: AN IMPORT SAYS WHICH SETTINGS IT BROUGHT WITH IT. Config stays in the source workbook and an import still applies it - that is deliberate and is what makes a plan reproducible from the file alone. What was missing was being told. A Config row is not like any other row in the file: every other sheet describes the PLAN, and replacing it is the point of an import, while Config describes how the plan is READ. Two of its settings switch calculation rules on and off and three more set the thresholds every allocation flag is measured against, so importing a colleague's workbook to look at their projects took their thresholds with it and every figure and flag on the screen shifted for a reason that was nowhere on it. Now the settings in force are captured before the model is replaced, compared by name afterwards, and any that differ are named on the banner with a screen of their own: what each one was, what it is now, and what it affects - calculation, flags or display only. Nothing is refused. It is a check, not a gate. Done in adopt(), which every import path funnels through - the web picker, the Python shell's open, a version restore and the difference report's apply - so it is asked once and asked of all of them. A first load has nothing to compare against and says nothing; a blank start counts as a baseline, because somebody who started blank, entered a plan and then imported over it is exactly who this is for. Also in this version: the reviewer confirmed that the display unit needs neither to survive an edit nor to reach the exported file - it is information while the application is open - so REQ-CAL-08 is unchanged and only the wording that read '3 informations' is corrected.</t>
+          <t>R-29, REQ-OUT-06: THE APPLICATION EXPORTS ITS ANSWERS AS WELL AS ITS QUESTIONS. Until now Export meant one thing - the plan, so it could come back - and there was no way to get the monthly figures out for a report, a spreadsheet or somebody else's model short of reading them off the screen. The export control is now a MENU with the choice on it: the plan as .xlsx or as the interchange file, both of which round-trip, or the CALCULATED MONTHLY FTE, which deliberately does not. Each item says which it is, so the choice can be made without trying it. The results workbook carries seven sheets: a ReadMe that states it cannot be imported and gives the formula; Summary, the Overall tab's tiles as figures; ProjectMonth and PersonMonth, one row each per month; DETAIL, one row per assignment per month carrying every term of the multiplication that produced it - period weight, the role factor before and after absorption, the number of sharers, the person weight and which row it came from, the month coverage; Flags, the over-allocated months and under-allocated runs; and Assumptions, the settings in force, marked for whether each one changed a figure or only its display. Two properties are held by test_results.py rather than asserted: every project-month and person-month is EXACTLY the sum of its Detail rows and all four totals in the file are the same number - the monthly sheets are summed FROM the detail rather than from the engine, so a reader who adds the column gets the total - and every Detail row reconciles to its own four numbers. The file covers what was ON SCREEN, horizon and filters included, and the ReadMe names them, so a file that has left the building can still say what it does and does not cover. The calculation now records each term as it works it out (calculate() returns `lines`), because an explanation assembled afterwards from the sheets could drift from the figure it claims to explain.</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -7782,12 +7782,12 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>R-26: THE NOTE ON capacity_unit WAS WRONG, and wrong in the way that matters - it named a value the application has never understood. It read "Display unit: 'FTE' or 'percent'"; the two values actually implemented are 'FTE' and 'hours', and anything else, 'percent' included, silently displays as FTE. So a user following the note would type a value, see nothing change, and have no way of telling whether they had misunderstood the setting or the setting was broken. The note now says what the unit IS: FTE is a WEIGHT, 1.00 being one person working a full month on the project, so ordinary values run about 0.1 to 1.0 - and 'hours' is that same weight multiplied by fte_hours_per_month. It also says the setting is display only. Corrected in the one place it is written and carried from there into the template, both dummy sets, the blank start's seed, this plan, the specification and the machine-readable contract. Template v1.11, dummies v1.13 and v1.5. No code and no figure changes. R-27, THE SAME REVIEW: the Configuration table no longer offers 'Delete' - or '+ row'. Nothing references a Config row, so V-17 had no hold on a deletion and nothing refused it; nothing reported it either, because every setting is read through a fallback to a built-in default. Measured on the 10x10 dummy with a house floor of 0.80 and the shared-role division turned off, deleting those two rows moved the total from 356.64 to 346.59 FTE-months and said nothing at all. Removing the control is a better answer than confirming it: there was never a good reason to press it, since the nine settings are read BY NAME and what a user changes is a VALUE, which stays as editable as any other cell. '+ row' goes with it because a row that can be created but never removed is a worse trap than the one being closed. New rule V-30 covers the case the control is no longer responsible for: a workbook that arrives without a setting, hand-edited or from a version that predates it, is told which default is in force.</t>
+          <t>R-28, REQ-IMP-14: AN IMPORT SAYS WHICH SETTINGS IT BROUGHT WITH IT. Config stays in the source workbook and an import still applies it - that is deliberate and is what makes a plan reproducible from the file alone. What was missing was being told. A Config row is not like any other row in the file: every other sheet describes the PLAN, and replacing it is the point of an import, while Config describes how the plan is READ. Two of its settings switch calculation rules on and off and three more set the thresholds every allocation flag is measured against, so importing a colleague's workbook to look at their projects took their thresholds with it and every figure and flag on the screen shifted for a reason that was nowhere on it. Now the settings in force are captured before the model is replaced, compared by name afterwards, and any that differ are named on the banner with a screen of their own: what each one was, what it is now, and what it affects - calculation, flags or display only. Nothing is refused. It is a check, not a gate. Done in adopt(), which every import path funnels through - the web picker, the Python shell's open, a version restore and the difference report's apply - so it is asked once and asked of all of them. A first load has nothing to compare against and says nothing; a blank start counts as a baseline, because somebody who started blank, entered a plan and then imported over it is exactly who this is for. Also in this version: the reviewer confirmed that the display unit needs neither to survive an edit nor to reach the exported file - it is information while the application is open - so REQ-CAL-08 is unchanged and only the wording that read '3 informations' is corrected.</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -7814,7 +7814,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>FIVE REVIEW POINTS, all about the application rather than the arithmetic - no figure moves. (1) R-21, REQ-IMP-12: A DATE COLUMN OFFERS A CALENDAR and stays typeable. Picking is what you want when the question is 'is the 14th a Tuesday'; typing is what you want on the twentieth row of a set you already know. So the panel is laid BESIDE the cell, never in front of it: the caret stays put, every key still reaches the cell, and what is typed steers the grid. Deliberately not &lt;input type=date&gt;, which would bring one editing model for text cells and another for dates. (2) R-22: THE PERIOD GENERATOR THAT FITS THE PROJECT. Auto derivation was offered on 'Others' projects, where it could only ever answer no - the rule hangs on CTA submission and the DB locks, which an internal project does not have and never will - and a control that refuses every time it is pressed teaches the reader the feature is broken. 'Others' is now offered Standard periods, which lays out Planning / Develop / Close with the dates blank; a trial not ready yet keeps the derivation, disabled, with the two missing milestones named, because that answer changes. The derivation itself was checked across all 62 dummy projects and is correct for all 50 trials. (3) R-23, REQ-DSH-13: THE APPLICATION DRAWS ITS OWN SCROLLBARS. Twice the browser was asked for a bar and twice it gave an overlay occupying no layout space - measured, a plain div with an explicit 14px ::-webkit-scrollbar still reports offsetHeight === clientHeight - so a table with eleven columns off to the right looked like one with none. Native scrolling is untouched. (4) R-24: THE STICKY BAND IS ONE ELEMENT, AND OPAQUE. Two independently sticky bars needed the second to know the height of the first, so a hairline ran between them that the page showed through, and at 92% opacity the rows underneath ghosted through the text. (5) R-25, REQ-IMP-13: WHAT AN ERROR IS ALLOWED TO DO is now a property of the rule, in three values. MUST refuses - something is wrong with the row itself. CONDITIONAL asks at Save, names what will be left unresolved and lets the user go ahead knowingly. INCOMPLETE reports and says nothing else - the row is still being built and asking would put a dialog in front of somebody every time they save a project they are half way through typing. The findings report and prap_io both label every error with its class.</t>
+          <t>R-26: THE NOTE ON capacity_unit WAS WRONG, and wrong in the way that matters - it named a value the application has never understood. It read "Display unit: 'FTE' or 'percent'"; the two values actually implemented are 'FTE' and 'hours', and anything else, 'percent' included, silently displays as FTE. So a user following the note would type a value, see nothing change, and have no way of telling whether they had misunderstood the setting or the setting was broken. The note now says what the unit IS: FTE is a WEIGHT, 1.00 being one person working a full month on the project, so ordinary values run about 0.1 to 1.0 - and 'hours' is that same weight multiplied by fte_hours_per_month. It also says the setting is display only. Corrected in the one place it is written and carried from there into the template, both dummy sets, the blank start's seed, this plan, the specification and the machine-readable contract. Template v1.11, dummies v1.13 and v1.5. No code and no figure changes. R-27, THE SAME REVIEW: the Configuration table no longer offers 'Delete' - or '+ row'. Nothing references a Config row, so V-17 had no hold on a deletion and nothing refused it; nothing reported it either, because every setting is read through a fallback to a built-in default. Measured on the 10x10 dummy with a house floor of 0.80 and the shared-role division turned off, deleting those two rows moved the total from 356.64 to 346.59 FTE-months and said nothing at all. Removing the control is a better answer than confirming it: there was never a good reason to press it, since the nine settings are read BY NAME and what a user changes is a VALUE, which stays as editable as any other cell. '+ row' goes with it because a row that can be created but never removed is a worse trap than the one being closed. New rule V-30 covers the case the control is no longer responsible for: a workbook that arrives without a setting, hand-edited or from a version that predates it, is told which default is in force.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>TWO REQUESTS. (1) R-19: THE ROLE/FACTOR CHECK REPORTS, AND STOPS REFUSING ROWS - and it is asked on the right composition. V-28 was retired at v2.32 for refusing data entry, but it was only the newest of three rules doing it: V-03 and V-23 refused as well, and for the same reason, so the complaint came straight back. All of them ask one question - has anybody entered a factor for this role - and the answer 'not yet' is a fact about the ASSUMPTIONS, a standing document maintained separately and often by somebody else. The person really is on the project. So both keep their severity, because the figures for that role really are wrong, and neither can refuse an edit any more. V-23 is also re-asked properly: it is now raised BY the calculation, keyed on the whole composition the lookup uses (project_type, clinical_phase, work_scope_type, period_name, role_name) and counted in the person-months that were actually calculated at 1.00. Asked off the sheets it walked every period of every project an assignment belonged to and demanded a row for each, including periods nobody was ever booked into. (2) R-20, REQ-CAL-17: THE PROJECT'S WINDOW COMES FROM ITS PERIODS, NOT ITS MILESTONES. Milestones are reference dates - the derivation reads them to lay the periods out, and several of them mark moments inside the run rather than its edges. Taking the window from them stretched the project over months belonging to no period at all, which are costed at weight 1.00, so the utilisation chart grew a flat shoulder at each end that no period justified. Now: the earliest period_start to the latest period_end, with a project that has no periods keeping its own typed dates because there is nothing to take a window from. Save writes the same window back, reading the periods the user TYPED and falling back to the milestone span where there are none - a derived period opens at the project's own start_date, so reading the saved window back from it would mean a wrong window could never correct itself. Figures move where the periods and the milestones disagreed: the 62-project dummy goes from 1,225 to 1,227 person-months.</t>
+          <t>FIVE REVIEW POINTS, all about the application rather than the arithmetic - no figure moves. (1) R-21, REQ-IMP-12: A DATE COLUMN OFFERS A CALENDAR and stays typeable. Picking is what you want when the question is 'is the 14th a Tuesday'; typing is what you want on the twentieth row of a set you already know. So the panel is laid BESIDE the cell, never in front of it: the caret stays put, every key still reaches the cell, and what is typed steers the grid. Deliberately not &lt;input type=date&gt;, which would bring one editing model for text cells and another for dates. (2) R-22: THE PERIOD GENERATOR THAT FITS THE PROJECT. Auto derivation was offered on 'Others' projects, where it could only ever answer no - the rule hangs on CTA submission and the DB locks, which an internal project does not have and never will - and a control that refuses every time it is pressed teaches the reader the feature is broken. 'Others' is now offered Standard periods, which lays out Planning / Develop / Close with the dates blank; a trial not ready yet keeps the derivation, disabled, with the two missing milestones named, because that answer changes. The derivation itself was checked across all 62 dummy projects and is correct for all 50 trials. (3) R-23, REQ-DSH-13: THE APPLICATION DRAWS ITS OWN SCROLLBARS. Twice the browser was asked for a bar and twice it gave an overlay occupying no layout space - measured, a plain div with an explicit 14px ::-webkit-scrollbar still reports offsetHeight === clientHeight - so a table with eleven columns off to the right looked like one with none. Native scrolling is untouched. (4) R-24: THE STICKY BAND IS ONE ELEMENT, AND OPAQUE. Two independently sticky bars needed the second to know the height of the first, so a hairline ran between them that the page showed through, and at 92% opacity the rows underneath ghosted through the text. (5) R-25, REQ-IMP-13: WHAT AN ERROR IS ALLOWED TO DO is now a property of the rule, in three values. MUST refuses - something is wrong with the row itself. CONDITIONAL asks at Save, names what will be left unresolved and lets the user go ahead knowingly. INCOMPLETE reports and says nothing else - the row is still being built and asking would put a dialog in front of somebody every time they save a project they are half way through typing. The findings report and prap_io both label every error with its class.</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -7878,12 +7878,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>R-18: V-28 IS RETIRED, one version after it was added, because of what it did rather than what it said. An error refuses the edit that raised it (REQ-IMP-09) - that is deliberate and stays - and V-28 was the first error about the ASSUMPTIONS that could fire on a project with no periods. So it fired while a project was still being built, which is exactly when its assignments are typed in: a user could not record who was on the project until RoleFactor already carried a factor for their role. That is backwards. The plan is the document being written; the assumptions are a standing document maintained separately, often by somebody else, and entering the plan must not wait on them. The gap V-28 filled is real and is not being denied: V-03 still refuses a role that is not valid for the project type, and V-23 still reports a role with no factor for a period the project spans - the same finding, at the point where the user can act on it. V-27 is unchanged: it is about the project's own type, phase and scope, which are on the row being edited, and the delivered defaults cover every combination the value lists offer, so it does not stand between a user and their own data. REQ-CAL-16 and the absorption arithmetic are untouched - no figure moves.</t>
+          <t>TWO REQUESTS. (1) R-19: THE ROLE/FACTOR CHECK REPORTS, AND STOPS REFUSING ROWS - and it is asked on the right composition. V-28 was retired at v2.32 for refusing data entry, but it was only the newest of three rules doing it: V-03 and V-23 refused as well, and for the same reason, so the complaint came straight back. All of them ask one question - has anybody entered a factor for this role - and the answer 'not yet' is a fact about the ASSUMPTIONS, a standing document maintained separately and often by somebody else. The person really is on the project. So both keep their severity, because the figures for that role really are wrong, and neither can refuse an edit any more. V-23 is also re-asked properly: it is now raised BY the calculation, keyed on the whole composition the lookup uses (project_type, clinical_phase, work_scope_type, period_name, role_name) and counted in the person-months that were actually calculated at 1.00. Asked off the sheets it walked every period of every project an assignment belonged to and demanded a row for each, including periods nobody was ever booked into. (2) R-20, REQ-CAL-17: THE PROJECT'S WINDOW COMES FROM ITS PERIODS, NOT ITS MILESTONES. Milestones are reference dates - the derivation reads them to lay the periods out, and several of them mark moments inside the run rather than its edges. Taking the window from them stretched the project over months belonging to no period at all, which are costed at weight 1.00, so the utilisation chart grew a flat shoulder at each end that no period justified. Now: the earliest period_start to the latest period_end, with a project that has no periods keeping its own typed dates because there is nothing to take a window from. Save writes the same window back, reading the periods the user TYPED and falling back to the milestone span where there are none - a derived period opens at the project's own start_date, so reading the saved window back from it would mean a wrong window could never correct itself. Figures move where the periods and the milestones disagreed: the 62-project dummy goes from 1,225 to 1,227 person-months.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -7910,7 +7910,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>TWO REQUESTS, and the second changes figures. (1) CROSS-CHECKS BETWEEN THE ASSUMPTIONS AND THE DATA: V-27 reports a project whose type, phase and work scope have no PeriodWeightStandard rows at all, and V-28 a role given to somebody on an assignment that has no RoleFactor rows at all. V-19 and V-23 already checked both, precisely - but only for periods a project actually HAS, so a project whose milestones are missing was never checked, and a combination nobody had entered was reported once per period rather than once as the one thing wrong. These ask the blunter question first, on the project. (2) R-17, REQ-CAL-16: WHERE NOBODY HOLDS A ROLE, its factor is absorbed by the role named to cover for it. A trial with no Clinical Data Associator still has the data to handle; it lands on the lead data manager, and a project costed without it looks cheaper than it is. Counted per month; one hop only; and WHICH ROLE COVERS FOR WHICH IS DATA - the new column RoleFactor.absorbed_by - because REQ-CAL-06 has said since the first plan that factors live in the workbook and never in the program. V-29 reports the case the rule cannot fix: an unstaffed role that nothing covers for, where the under-estimate remains and nothing else would mention it. Schema 7 to 8. A fifth of the dummy's projects now run without one of those roles, so the rule is under the four-way comparison rather than in one unit test.</t>
+          <t>R-18: V-28 IS RETIRED, one version after it was added, because of what it did rather than what it said. An error refuses the edit that raised it (REQ-IMP-09) - that is deliberate and stays - and V-28 was the first error about the ASSUMPTIONS that could fire on a project with no periods. So it fired while a project was still being built, which is exactly when its assignments are typed in: a user could not record who was on the project until RoleFactor already carried a factor for their role. That is backwards. The plan is the document being written; the assumptions are a standing document maintained separately, often by somebody else, and entering the plan must not wait on them. The gap V-28 filled is real and is not being denied: V-03 still refuses a role that is not valid for the project type, and V-23 still reports a role with no factor for a period the project spans - the same finding, at the point where the user can act on it. V-27 is unchanged: it is about the project's own type, phase and scope, which are on the row being edited, and the delivered defaults cover every combination the value lists offer, so it does not stand between a user and their own data. REQ-CAL-16 and the absorption arithmetic are untouched - no figure moves.</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -7942,12 +7942,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>R-16, SCHEMA 7: outsourcing_type becomes outsourcing_scope_det, and becomes FREE TEXT. Schema 6 put work_scope_type in the weights and left outsourcing_type beside it as a second controlled vocabulary on the same axis - two fields to keep in step, one of which decided nothing. It is now a note in the requester's own words: what is outsourced and to whom, the detail a category cannot carry. Three things follow. V-25 is RETIRED, because it existed only to police the two against each other and can no longer fire. The dashboard's scope filter moves to work_scope_type, since a drop-down built from whatever sentences people have typed is not a filter - and the field it used to offer is the one that no longer decides anything. And a workbook still carrying outsourcing_type is READ rather than refused: the column is renamed on the way in and the application says so once, because a rename is the one schema change that otherwise loses a filled-in column in silence.</t>
+          <t>TWO REQUESTS, and the second changes figures. (1) CROSS-CHECKS BETWEEN THE ASSUMPTIONS AND THE DATA: V-27 reports a project whose type, phase and work scope have no PeriodWeightStandard rows at all, and V-28 a role given to somebody on an assignment that has no RoleFactor rows at all. V-19 and V-23 already checked both, precisely - but only for periods a project actually HAS, so a project whose milestones are missing was never checked, and a combination nobody had entered was reported once per period rather than once as the one thing wrong. These ask the blunter question first, on the project. (2) R-17, REQ-CAL-16: WHERE NOBODY HOLDS A ROLE, its factor is absorbed by the role named to cover for it. A trial with no Clinical Data Associator still has the data to handle; it lands on the lead data manager, and a project costed without it looks cheaper than it is. Counted per month; one hop only; and WHICH ROLE COVERS FOR WHICH IS DATA - the new column RoleFactor.absorbed_by - because REQ-CAL-06 has said since the first plan that factors live in the workbook and never in the program. V-29 reports the case the rule cannot fix: an unstaffed role that nothing covers for, where the under-estimate remains and nothing else would mention it. Schema 7 to 8. A fifth of the dummy's projects now run without one of those roles, so the rule is under the four-way comparison rather than in one unit test.</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -7974,7 +7974,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>R-15, REQ-CAL-15: BOTH ASSIGNMENT DATES ARE OPTIONAL, and a blank one means the project's own. Most people are on a project for the whole of it, and requiring two dates that simply repeat the project's asks somebody to copy the same pair onto every row and then keep them in step when the project moves. The end date already worked this way; the start did not, and a blank one was the worst of the three possible behaviours - the assignment contributed NOTHING, the person looked unassigned, and no finding said why. The window is now computed by one function shared by the calculation and by the role-sharing pre-pass, so the months a person is counted IN cannot differ from the months they are counted AMONG; an undated person is a sharer like any other. Roughly a third of the dummy fixture now leaves both dates blank, which is what a real file looks like and puts the inherited window under the four-way comparison rather than in one unit test.</t>
+          <t>R-16, SCHEMA 7: outsourcing_type becomes outsourcing_scope_det, and becomes FREE TEXT. Schema 6 put work_scope_type in the weights and left outsourcing_type beside it as a second controlled vocabulary on the same axis - two fields to keep in step, one of which decided nothing. It is now a note in the requester's own words: what is outsourced and to whom, the detail a category cannot carry. Three things follow. V-25 is RETIRED, because it existed only to police the two against each other and can no longer fire. The dashboard's scope filter moves to work_scope_type, since a drop-down built from whatever sentences people have typed is not a filter - and the field it used to offer is the one that no longer decides anything. And a workbook still carrying outsourcing_type is READ rather than refused: the column is renamed on the way in and the application says so once, because a rename is the one schema change that otherwise loses a filled-in column in silence.</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -8006,12 +8006,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>TWO CHANGES, BOTH REQUESTED, AND THE FIRST CHANGES EVERY FIGURE A SHARED ROLE EVER PRODUCED. (1) R-13, REQ-CAL-14: where several people hold the same role on the same project in the same month, the role factor is DIVIDED BETWEEN THEM. The factor states what the ROLE costs the project in that period, not what each holder costs, so until now a trial staffed by two data managers cost twice a trial staffed by one - the same work, priced by how many people were named against it. Counted per month, so a sharer leaving restores the others without an edit; by distinct people, so one person on two rows is one person; and each person's own weight still applies to their share. Kept as the setting split_shared_role_fte, default 1, so a figure produced before this rule can still be reproduced and compared. (2) R-14: THE DELIVERED DEFAULTS. PeriodWeightStandard and RoleFactor arrived empty in the template and were filled with a placeholder 1.00 by a blank start - and 1.00 everywhere is not a starting point, it is the absence of one: at 1.00 the period weight and the role factor cancel out of the arithmetic entirely, so the application produced figures that looked like an answer and were not. Both now arrive filled in - 84 period weights and 429 role factors - defined once and read by the template, the blank start and the dummy datasets alike, so the workbook and the application hold the same assumptions by construction. check_consistency.py fails if they drift, and fails too if the figures ever revert to one flat value. A defect was found while testing: prap_io read Config with `or default`, so a setting deliberately set to 0 silently came back on.</t>
+          <t>R-15, REQ-CAL-15: BOTH ASSIGNMENT DATES ARE OPTIONAL, and a blank one means the project's own. Most people are on a project for the whole of it, and requiring two dates that simply repeat the project's asks somebody to copy the same pair onto every row and then keep them in step when the project moves. The end date already worked this way; the start did not, and a blank one was the worst of the three possible behaviours - the assignment contributed NOTHING, the person looked unassigned, and no finding said why. The window is now computed by one function shared by the calculation and by the role-sharing pre-pass, so the months a person is counted IN cannot differ from the months they are counted AMONG; an undated person is a sharer like any other. Roughly a third of the dummy fixture now leaves both dates blank, which is what a real file looks like and puts the inherited window under the four-way comparison rather than in one unit test.</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -8038,12 +8038,12 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>SCHEMA 6 - THE WORK SCOPE, AND THE BIOSIMILAR SPLIT. Requested 2026-08-20, and the first change to the data model since the plan was baselined. (1) work_scope_type joins PeriodWeightStandard and RoleFactor beside clinical_phase, and the keys become (project_type, clinical_phase, work_scope_type, period_name) and that plus role_name. How much of the work is kept in-house changes how much of it lands on this team, and until now the model had nowhere to say so. (2) A ROW WITH AN EMPTY work_scope_type APPLIES TO EVERY SCOPE, and a project falls back to it when there is no row for its own scope. That is a judgment made here rather than requested: without it RoleFactor is 1,269 hand-entered rows instead of 429, two thirds of them repeating their neighbour, and every schema 5 file would stop calculating on the day it was opened. With it, a schema 5 file's rows ARE the every-scope rows and keep working. (3) Project gains work_scope_type, because the key selects a row FOR A PROJECT and nothing could choose between the three scope rows without it - implied by the request rather than stated in it. outsourcing_type stays, descriptive, and V-25 reports the two contradicting each other. (4) 'Biosimilar CT' becomes 'Biosimilar CT (Healthy)' and 'Biosimilar CT (Patient)'. A project type is now recognised as a clinical trial by the START of its name, so the next subdivision is a value-list change rather than a code change. V-26 reports the retired value with the two it became, because only the reader knows which of them a given trial was. Template v1.8, dummies v1.10 and v1.2.</t>
+          <t>TWO CHANGES, BOTH REQUESTED, AND THE FIRST CHANGES EVERY FIGURE A SHARED ROLE EVER PRODUCED. (1) R-13, REQ-CAL-14: where several people hold the same role on the same project in the same month, the role factor is DIVIDED BETWEEN THEM. The factor states what the ROLE costs the project in that period, not what each holder costs, so until now a trial staffed by two data managers cost twice a trial staffed by one - the same work, priced by how many people were named against it. Counted per month, so a sharer leaving restores the others without an edit; by distinct people, so one person on two rows is one person; and each person's own weight still applies to their share. Kept as the setting split_shared_role_fte, default 1, so a figure produced before this rule can still be reproduced and compared. (2) R-14: THE DELIVERED DEFAULTS. PeriodWeightStandard and RoleFactor arrived empty in the template and were filled with a placeholder 1.00 by a blank start - and 1.00 everywhere is not a starting point, it is the absence of one: at 1.00 the period weight and the role factor cancel out of the arithmetic entirely, so the application produced figures that looked like an answer and were not. Both now arrive filled in - 84 period weights and 429 role factors - defined once and read by the template, the blank start and the dummy datasets alike, so the workbook and the application hold the same assumptions by construction. check_consistency.py fails if they drift, and fails too if the figures ever revert to one flat value. A defect was found while testing: prap_io read Config with `or default`, so a setting deliberately set to 0 silently came back on.</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -8070,12 +8070,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 25, application v1.24. (1) EVERY FILTER NOW TAKES SEVERAL VALUES AT ONCE. Each is a drop-down of tick boxes built on &lt;details&gt;, which gives open, close, keyboard operation and focus for nothing; a plain &lt;select multiple&gt; would have cost seven tall boxes across the bar and asked the reader to know that ctrl-click means 'and also'. Nothing ticked means All, which is what the closed control says, so the bar reads as it did with single selects; one ticked reads as that value, more than one as a count with the full list on hover. Values within one filter are an OR - ticking a second project type WIDENS the view - while the filters remain an AND with each other, which is the only reading that makes 'NewDrug CT and Others, in-house' mean anything. Each has its own Clear; Reset still empties them all; and a value that has gone from the file is dropped from the selection, since the page must not stay filtered by something the reader can no longer see. (2) AUTO DERIVATION in the Periods section builds a project's periods from its milestones by the rule on sheet 05, and (3) BLANK LIST in the Milestones section lays out the ten standard milestone names with their dates empty, so only the dates have to be typed. Both produce ORDINARY ROWS - provisional until Save, editable and deletable afterwards, subject to every rule - because the point is to save the typing, not to take the decision away. Auto derivation reads the milestones from the raw sheet so a set just typed and not yet saved still counts, which is the ordinary case when the two buttons are used one after the other; it asks before replacing an existing set; and it refuses what it cannot do, naming the reason: an 'Others' project (the rule hangs on CTA submission and the DB locks) or a trial missing either of those (V-16). Blank list does not repeat a name already listed, since a second 'CTA submission' is the duplicate V-20 exists to catch. A LATENT CRASH was found while testing them and fixed: clicking a row that had not been saved yet made its identifier the selection, and the detail panels below need a RECORD - dates, a name, a calculation - which a draft has none of. projDetail threw, taking the whole re-render with it, so the click appeared to do nothing at all. Both detail panels now fall back to the scratch panels built for exactly that state. tools/test_generate.py checks the derivation against the rule term by term on a project built to exercise every branch. No requirement, rule, calculation or schema version changed.</t>
+          <t>SCHEMA 6 - THE WORK SCOPE, AND THE BIOSIMILAR SPLIT. Requested 2026-08-20, and the first change to the data model since the plan was baselined. (1) work_scope_type joins PeriodWeightStandard and RoleFactor beside clinical_phase, and the keys become (project_type, clinical_phase, work_scope_type, period_name) and that plus role_name. How much of the work is kept in-house changes how much of it lands on this team, and until now the model had nowhere to say so. (2) A ROW WITH AN EMPTY work_scope_type APPLIES TO EVERY SCOPE, and a project falls back to it when there is no row for its own scope. That is a judgment made here rather than requested: without it RoleFactor is 1,269 hand-entered rows instead of 429, two thirds of them repeating their neighbour, and every schema 5 file would stop calculating on the day it was opened. With it, a schema 5 file's rows ARE the every-scope rows and keep working. (3) Project gains work_scope_type, because the key selects a row FOR A PROJECT and nothing could choose between the three scope rows without it - implied by the request rather than stated in it. outsourcing_type stays, descriptive, and V-25 reports the two contradicting each other. (4) 'Biosimilar CT' becomes 'Biosimilar CT (Healthy)' and 'Biosimilar CT (Patient)'. A project type is now recognised as a clinical trial by the START of its name, so the next subdivision is a value-list change rather than a code change. V-26 reports the retired value with the two it became, because only the reader knows which of them a given trial was. Template v1.8, dummies v1.10 and v1.2.</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -8122,19 +8122,19 @@
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 24, application v1.23. Three changes to the filter bar and to what the unsaved-change counter can tell you. (1) OUTSOURCING TYPE joins the filter conditions, driving the same machinery as the other six - the charts, both Overall tables and the source-data tabs - and Reset puts it back with the rest. (2) THE HORIZON NOW FOLLOWS THE FILTERS. Narrowing to one project type left the window the whole portfolio needed, so a two-year span went mostly empty and the reader was looking at a chart of nothing with no way to tell whether that was the answer or the view. Changing a filter now pulls From and To in to the months the surviving rows actually reach. Two things are deliberately left alone: a combination that matches NOTHING keeps the window where it was, because jumping to an arbitrary span would hide the reason the screen is empty; and typing in From or To is the user moving the window themselves, so the re-fit runs only when a filter DROPDOWN moves. (3) A SHOW DETAILS button beside the counter opens every change waiting to be saved, as a table: the time it happened, which tab, which section, which row, which item, what it was before and what it is now. Newest first, because the question it answers is almost always 'what did I just do' - the edit you are unsure about is the one you made a moment ago - and the first row is tinted for the same reason. The dialog closes, goes full screen for a log too wide or too long for the ordinary box, and scrolls with the same visible bar and edge shading as every other scroll region. The section column shows the name the panel goes by on screen rather than the sheet name, because the point of the log is being able to walk back to the thing you changed; the sheet is still what is recorded underneath. Every pending entry now carries the time it was made, which nothing did before. tools/test_filters.py covers all three. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 25, application v1.24. (1) EVERY FILTER NOW TAKES SEVERAL VALUES AT ONCE. Each is a drop-down of tick boxes built on &lt;details&gt;, which gives open, close, keyboard operation and focus for nothing; a plain &lt;select multiple&gt; would have cost seven tall boxes across the bar and asked the reader to know that ctrl-click means 'and also'. Nothing ticked means All, which is what the closed control says, so the bar reads as it did with single selects; one ticked reads as that value, more than one as a count with the full list on hover. Values within one filter are an OR - ticking a second project type WIDENS the view - while the filters remain an AND with each other, which is the only reading that makes 'NewDrug CT and Others, in-house' mean anything. Each has its own Clear; Reset still empties them all; and a value that has gone from the file is dropped from the selection, since the page must not stay filtered by something the reader can no longer see. (2) AUTO DERIVATION in the Periods section builds a project's periods from its milestones by the rule on sheet 05, and (3) BLANK LIST in the Milestones section lays out the ten standard milestone names with their dates empty, so only the dates have to be typed. Both produce ORDINARY ROWS - provisional until Save, editable and deletable afterwards, subject to every rule - because the point is to save the typing, not to take the decision away. Auto derivation reads the milestones from the raw sheet so a set just typed and not yet saved still counts, which is the ordinary case when the two buttons are used one after the other; it asks before replacing an existing set; and it refuses what it cannot do, naming the reason: an 'Others' project (the rule hangs on CTA submission and the DB locks) or a trial missing either of those (V-16). Blank list does not repeat a name already listed, since a second 'CTA submission' is the duplicate V-20 exists to catch. A LATENT CRASH was found while testing them and fixed: clicking a row that had not been saved yet made its identifier the selection, and the detail panels below need a RECORD - dates, a name, a calculation - which a draft has none of. projDetail threw, taking the whole re-render with it, so the click appeared to do nothing at all. Both detail panels now fall back to the scratch panels built for exactly that state. tools/test_generate.py checks the derivation against the rule term by term on a project built to exercise every branch. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.26</t>
+          <t>Issued for review</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -8154,19 +8154,19 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 23, application v1.22. Four values that were typed by hand while the rows underneath already said what they should be. (1) A project's WINDOW is now recalculated on Save: start_date becomes the earliest of its milestone dates and end_date the latest, and total_period_months follows without anyone touching it. (2) planned_member_count becomes the number of DISTINCT people assigned to the project - people, not assignment rows, since one person may hold several. Both are done at SAVE rather than at load, deliberately: doing them at load would rewrite a workbook produced elsewhere the moment somebody opened it, and the delivered examples set a project start before its first milestone quite legitimately. At Save it is a consequence of an edit just made, and the banner names every value it changed. Two guards keep the change from destroying information: a project with NO milestone dates keeps the window that was typed, because there is nothing to derive it from; and a project with NO assignments keeps the team size that was typed, because 'nobody is assigned yet' is not the statement 'this needs nobody'. ONE CONSEQUENCE IS WORTH STATING: a project now ends at its last milestone, so work that legitimately continues past the final DB lock - close-out, archiving, an inspection - has to be carried by a milestone if it is to be inside the window, and an assignment running past it is reported as V-07. The period derivation already allowed for that headroom by running Close-out (final) to the later of the DB lock and the project end; deriving the end from the milestones removes it. (3) A new row in Periods is given the next PERIOD_SEQ for its project. The request named a 'period_id': the sheet has none, it is keyed on (project_id, period_name) per change R-11, and period_seq is the field that carries the order - so that is the number allocated, one past the highest in that project, exactly as milestone_seq is. (4) A weight-override window now shows the PROJECT and ROLE of its assignment even when that assignment has not been saved. It read them from the validated model, which excludes anything still being entered, so the two lookup columns went blank until Save - and they exist precisely so that, while typing, the user can confirm the window is attached to the right piece of work. They are read from the raw sheets now, and the same two columns were added to the scratch panel that a plan started blank uses. tools/test_derive.py covers all four; seven of its ten checks fail against the previous build. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 24, application v1.23. Three changes to the filter bar and to what the unsaved-change counter can tell you. (1) OUTSOURCING TYPE joins the filter conditions, driving the same machinery as the other six - the charts, both Overall tables and the source-data tabs - and Reset puts it back with the rest. (2) THE HORIZON NOW FOLLOWS THE FILTERS. Narrowing to one project type left the window the whole portfolio needed, so a two-year span went mostly empty and the reader was looking at a chart of nothing with no way to tell whether that was the answer or the view. Changing a filter now pulls From and To in to the months the surviving rows actually reach. Two things are deliberately left alone: a combination that matches NOTHING keeps the window where it was, because jumping to an arbitrary span would hide the reason the screen is empty; and typing in From or To is the user moving the window themselves, so the re-fit runs only when a filter DROPDOWN moves. (3) A SHOW DETAILS button beside the counter opens every change waiting to be saved, as a table: the time it happened, which tab, which section, which row, which item, what it was before and what it is now. Newest first, because the question it answers is almost always 'what did I just do' - the edit you are unsure about is the one you made a moment ago - and the first row is tinted for the same reason. The dialog closes, goes full screen for a log too wide or too long for the ordinary box, and scrolls with the same visible bar and edge shading as every other scroll region. The section column shows the name the panel goes by on screen rather than the sheet name, because the point of the log is being able to walk back to the thing you changed; the sheet is still what is recorded underneath. Every pending entry now carries the time it was made, which nothing did before. tools/test_filters.py covers all three. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.25</t>
+          <t>Superseded by v2.26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -8186,19 +8186,19 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 22, application v1.21. Three changes to what a new row arrives with, and to whether the reader can tell there is more to see. (1) IDENTIFIERS are now allocated on insert for project_id, person_id and milestone_seq as well as assignment_id, and the rule is ONE PAST THE HIGHEST already in the sheet rather than the smallest unused. The old rule was about tidiness - a file whose ids ran 1..46 and then jumped to 901 for a few hand-placed rows would not start climbing from 902; the new one is about being able to tell at a glance which rows were added today, and a gap left by a deleted row now stays a gap, which is how an identifier sequence behaves everywhere else. milestone_seq counts within its own PROJECT, not across the file, because that is the list it orders. (2) WEIGHTS start at 1.00: ProjectPeriod.weight, Person.capacity_fte, Assignment.person_weight and PersonPeriodWeight.weight_override. 1.00 is the neutral multiplier, and the alternative is not 'no value' but ZERO - an empty weight reads as 0.00 in the calculation, so a row left alone contributed nothing at all and nothing on screen said so. A row that contributes too much is noticed; a row that contributes nothing is not. This required a second concept alongside 'blank': a row carrying only the values the APPLICATION put there is still an empty row, so Save does not promote it and Export refuses to write it - otherwise every insert would immediately become a half-record complaining about what it is missing. (3) SCROLL REGIONS now say which way there is more. Every section was already bounded on both axes, but scrollbar-width:thin bought a browser OVERLAY bar that occupies no layout space and fades when idle - measured, offsetWidth === clientWidth - so a table with eleven columns off to the right looked exactly like a table with none. The bar is now a real 12px with a visible thumb; and because overlay scrollbars are the default on some platforms whatever the CSS asks for, each region ALSO carries a soft shade on any edge that has content beyond it, drawn over the box so table rows cannot paint on top of it, and removed the moment that edge is reached so it always means 'more this way'. tools/test_newrow.py covers all three. Two existing tests had to change, and both were encoding old behaviour rather than finding new faults: test_rows was promoting an override row with no window and no weight in it, which isSkeleton now declines to do, and test_nokey could no longer reach a keyless row by skipping the identifier - the application supplies one - so it clears it explicitly instead. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 23, application v1.22. Four values that were typed by hand while the rows underneath already said what they should be. (1) A project's WINDOW is now recalculated on Save: start_date becomes the earliest of its milestone dates and end_date the latest, and total_period_months follows without anyone touching it. (2) planned_member_count becomes the number of DISTINCT people assigned to the project - people, not assignment rows, since one person may hold several. Both are done at SAVE rather than at load, deliberately: doing them at load would rewrite a workbook produced elsewhere the moment somebody opened it, and the delivered examples set a project start before its first milestone quite legitimately. At Save it is a consequence of an edit just made, and the banner names every value it changed. Two guards keep the change from destroying information: a project with NO milestone dates keeps the window that was typed, because there is nothing to derive it from; and a project with NO assignments keeps the team size that was typed, because 'nobody is assigned yet' is not the statement 'this needs nobody'. ONE CONSEQUENCE IS WORTH STATING: a project now ends at its last milestone, so work that legitimately continues past the final DB lock - close-out, archiving, an inspection - has to be carried by a milestone if it is to be inside the window, and an assignment running past it is reported as V-07. The period derivation already allowed for that headroom by running Close-out (final) to the later of the DB lock and the project end; deriving the end from the milestones removes it. (3) A new row in Periods is given the next PERIOD_SEQ for its project. The request named a 'period_id': the sheet has none, it is keyed on (project_id, period_name) per change R-11, and period_seq is the field that carries the order - so that is the number allocated, one past the highest in that project, exactly as milestone_seq is. (4) A weight-override window now shows the PROJECT and ROLE of its assignment even when that assignment has not been saved. It read them from the validated model, which excludes anything still being entered, so the two lookup columns went blank until Save - and they exist precisely so that, while typing, the user can confirm the window is attached to the right piece of work. They are read from the raw sheets now, and the same two columns were added to the scratch panel that a plan started blank uses. tools/test_derive.py covers all four; seven of its ten checks fail against the previous build. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.24</t>
+          <t>Superseded by v2.25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -8218,19 +8218,19 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 21, application v1.20. A ROW WITH NO IDENTIFIER IS NO LONGER TREATED AS A RECORD, which fixes three reported faults that were all one fault. A project saved with every field filled in EXCEPT project_id was indexed as M.projects[null] - and JavaScript turns a null key into the STRING 'null'. The application then believed in a project called 'null'. It became the selection; and the row filter, which keeps a row when the set of visible project_ids contains it, compared the set {'null'} against the row's actual null and missed - so the Projects table the user had just typed into reported 'No rows. Use + row to add one.' The Milestones and Periods sections beneath went looking for a parent named 'null', found none, and reported the same; a row added there would have been stamped 'null' and lost. A person saved without a person_id did exactly the same, which is why the Assignments and Weight overrides sections beneath them offered nothing to fill in. One cause, three symptoms, on both tabs. The rule now is explicit: a row becomes a RECORD when it carries its sheet's identifier and not before. Until then it is not indexed, it is reported as an error naming the column to fill in, and Save is refused rather than silently creating the phantom - which matches the export guard, that has always refused to write such a row. Crucially the row STAYS ON SCREEN, because it is the row the user is in the middle of repairing: both the project and people tables keep any row that has no identifier alongside the real ones, and a child table now shows a row carrying no parent key wherever the user is, since a row that cannot be seen cannot be repaired or deleted, only silently dropped. Supplying the identifier recovers completely. The same rule went into tools/prap_io.py, so the command line and the page still report the same findings. tools/test_nokey.py covers all of it for a project, for a person, and for a workbook that already carries such a row; four of its eleven checks fail against the previous build, reproducing the reported symptoms exactly - '0 rows on screen', projects=['null'], and 'No rows. Use + row to add one.' No requirement, calculation or schema version changed.</t>
+          <t>Gate 4 round 22, application v1.21. Three changes to what a new row arrives with, and to whether the reader can tell there is more to see. (1) IDENTIFIERS are now allocated on insert for project_id, person_id and milestone_seq as well as assignment_id, and the rule is ONE PAST THE HIGHEST already in the sheet rather than the smallest unused. The old rule was about tidiness - a file whose ids ran 1..46 and then jumped to 901 for a few hand-placed rows would not start climbing from 902; the new one is about being able to tell at a glance which rows were added today, and a gap left by a deleted row now stays a gap, which is how an identifier sequence behaves everywhere else. milestone_seq counts within its own PROJECT, not across the file, because that is the list it orders. (2) WEIGHTS start at 1.00: ProjectPeriod.weight, Person.capacity_fte, Assignment.person_weight and PersonPeriodWeight.weight_override. 1.00 is the neutral multiplier, and the alternative is not 'no value' but ZERO - an empty weight reads as 0.00 in the calculation, so a row left alone contributed nothing at all and nothing on screen said so. A row that contributes too much is noticed; a row that contributes nothing is not. This required a second concept alongside 'blank': a row carrying only the values the APPLICATION put there is still an empty row, so Save does not promote it and Export refuses to write it - otherwise every insert would immediately become a half-record complaining about what it is missing. (3) SCROLL REGIONS now say which way there is more. Every section was already bounded on both axes, but scrollbar-width:thin bought a browser OVERLAY bar that occupies no layout space and fades when idle - measured, offsetWidth === clientWidth - so a table with eleven columns off to the right looked exactly like a table with none. The bar is now a real 12px with a visible thumb; and because overlay scrollbars are the default on some platforms whatever the CSS asks for, each region ALSO carries a soft shade on any edge that has content beyond it, drawn over the box so table rows cannot paint on top of it, and removed the moment that edge is reached so it always means 'more this way'. tools/test_newrow.py covers all three. Two existing tests had to change, and both were encoding old behaviour rather than finding new faults: test_rows was promoting an override row with no window and no weight in it, which isSkeleton now declines to do, and test_nokey could no longer reach a keyless row by skipping the identifier - the application supplies one - so it clears it explicitly instead. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.23</t>
+          <t>Superseded by v2.24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -8250,19 +8250,19 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 20, application v1.19. SCROLL POSITION now survives a re-render. Committing a cell re-renders the panel it lives in, and a freshly built element starts at the top left - so filling one cell in a table twenty-two columns wide sent every scroll box back to the first row and the first column, and the next cell the user meant to fill was off screen again. On a dashboard that is invisible; during data entry it costs a re-scroll for every single cell, which is the difference between a usable table and an unusable one. It showed up as soon as a plan could be typed in from scratch (round 18) because that is the first time anyone fills in cells one after another. Every scroll offset on the page is now captured and put back around each re-render, along with the page's own scroll position, which a re-render can also move because the edit banner changes height between 'no changes' and 'n changes not yet saved'. The key has to survive the DOM being rebuilt: a data table names itself by its sheet, and everything else - the charts - is keyed by where it sits among the other keyless boxes in its own pane. The same wrapper covers the three other places that redraw part of the page: selecting a parent row, selecting an assignment, and the matrix/rows toggle on General assumptions. Changing TAB still takes the page to the top, because that is the user moving somewhere else rather than the page moving underneath them. tools/test_scroll.py drives the real browser and checks all four commit paths, the page scroll, a row 900px down a 289-row table, and that the cell just filled is still on screen afterwards; five of its eleven checks fail against the previous build. The test itself needed care: Playwright's own click scrolls its target into view first, and Chromium's scrollIntoView scrolls EVERY scrollable ancestor, so a naive click on an off-screen cell moves the box before the application has run a line - the first draft of the test was measuring the driver rather than the page. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 21, application v1.20. A ROW WITH NO IDENTIFIER IS NO LONGER TREATED AS A RECORD, which fixes three reported faults that were all one fault. A project saved with every field filled in EXCEPT project_id was indexed as M.projects[null] - and JavaScript turns a null key into the STRING 'null'. The application then believed in a project called 'null'. It became the selection; and the row filter, which keeps a row when the set of visible project_ids contains it, compared the set {'null'} against the row's actual null and missed - so the Projects table the user had just typed into reported 'No rows. Use + row to add one.' The Milestones and Periods sections beneath went looking for a parent named 'null', found none, and reported the same; a row added there would have been stamped 'null' and lost. A person saved without a person_id did exactly the same, which is why the Assignments and Weight overrides sections beneath them offered nothing to fill in. One cause, three symptoms, on both tabs. The rule now is explicit: a row becomes a RECORD when it carries its sheet's identifier and not before. Until then it is not indexed, it is reported as an error naming the column to fill in, and Save is refused rather than silently creating the phantom - which matches the export guard, that has always refused to write such a row. Crucially the row STAYS ON SCREEN, because it is the row the user is in the middle of repairing: both the project and people tables keep any row that has no identifier alongside the real ones, and a child table now shows a row carrying no parent key wherever the user is, since a row that cannot be seen cannot be repaired or deleted, only silently dropped. Supplying the identifier recovers completely. The same rule went into tools/prap_io.py, so the command line and the page still report the same findings. tools/test_nokey.py covers all of it for a project, for a person, and for a workbook that already carries such a row; four of its eleven checks fail against the previous build, reproducing the reported symptoms exactly - '0 rows on screen', projects=['null'], and 'No rows. Use + row to add one.' No requirement, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.22</t>
+          <t>Superseded by v2.23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -8282,19 +8282,19 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 19, application v1.18. The four CHILD sections are now on screen from the moment a blank plan is started, and can be filled in before their parent is saved. Round 18 made a plan enterable but only in one order: the project tab showed the Projects table alone until a project had been saved, and the person tab the People table alone. Both were literally true - the detail panels need a parent RECORD, with dates for the timeline and a name for every heading, and a row still being typed is not even parsed into the model - but the consequence was that Milestones, Periods, Assignments and Weight overrides were invisible to anyone building their first plan. A section that appears only after you have done something else reads as a section that does not exist. So the tables are drawn from the start, in the same two-column arrangement they have when a workbook is loaded, and they behave in three states. With no parent at all they are LOCKED and carry the reason where the '+ row' button would be, because a child row whose parent does not exist has nothing to attach to and would be dropped when the file is read back - saying so beats offering a button that creates a row nobody can rescue. The moment the parent row carries an IDENTIFIER - before it is saved - they unlock and scope themselves to it, so a plan can be entered the way a person actually thinks about one: the project and its milestones together, the person and their assignments together, each committed in a single Save. Two fixes were needed for that to work. The draft row now becomes the tab's selection, since child rows inherit their parent key from the selection and without it they were created parentless. And the fallback that finds the assignment for a new override row now reads the raw sheet rather than the validated array: the validated array excludes anything still being entered, so on a plan being typed from scratch the only assignment on screen was not found. tools/test_blank.py now enters the milestones BEFORE saving the project and the assignment BEFORE saving the person, checks each child inherited the right foreign key, and adds a weight override window to prove the fourth section works and REPLACES the person weight for its three months and no others. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 20, application v1.19. SCROLL POSITION now survives a re-render. Committing a cell re-renders the panel it lives in, and a freshly built element starts at the top left - so filling one cell in a table twenty-two columns wide sent every scroll box back to the first row and the first column, and the next cell the user meant to fill was off screen again. On a dashboard that is invisible; during data entry it costs a re-scroll for every single cell, which is the difference between a usable table and an unusable one. It showed up as soon as a plan could be typed in from scratch (round 18) because that is the first time anyone fills in cells one after another. Every scroll offset on the page is now captured and put back around each re-render, along with the page's own scroll position, which a re-render can also move because the edit banner changes height between 'no changes' and 'n changes not yet saved'. The key has to survive the DOM being rebuilt: a data table names itself by its sheet, and everything else - the charts - is keyed by where it sits among the other keyless boxes in its own pane. The same wrapper covers the three other places that redraw part of the page: selecting a parent row, selecting an assignment, and the matrix/rows toggle on General assumptions. Changing TAB still takes the page to the top, because that is the user moving somewhere else rather than the page moving underneath them. tools/test_scroll.py drives the real browser and checks all four commit paths, the page scroll, a row 900px down a 289-row table, and that the cell just filled is still on screen afterwards; five of its eleven checks fail against the previous build. The test itself needed care: Playwright's own click scrolls its target into view first, and Chromium's scrollIntoView scrolls EVERY scrollable ancestor, so a naive click on an off-screen cell moves the box before the application has run a line - the first draft of the test was measuring the driver rather than the page. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.21</t>
+          <t>Superseded by v2.22</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -8314,19 +8314,19 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 18, application v1.17. A PLAN CAN NOW BE STARTED IN THE APPLICATION ITSELF. The landing screen offers two ways in, given equal weight: load a source workbook, or start blank and type. 'Start blank' opens every tab and every section an upload opens - it is the same code path, so it is not a lesser mode with its own rules - and the plan it produces exports to the same .xlsx as any other. A blank start is not an EMPTY workbook: with no Lists sheet there would be no vocabulary, so every typed value would be reported as unrecognised (V-11) and no field could offer a choice, and with no Config there would be no thresholds. It therefore begins from the reference content of the delivered template, embedded in the HTML by tools/build_app_seed.py and held to the template by check_consistency.py. The PeriodFTEStandard and RoleFactor grids are NOT embedded: the application builds them from the value lists it was just seeded with - 56 standard weights and 289 role factors, every combination a project can reach - so a company that adds a role to Lists gets it without anybody regenerating anything. Every seeded figure is a placeholder 1.00 that says so on its own row, because an invented weight that looks like a company standard is worse than an obvious placeholder: only one of the two gets questioned. Four things had to be fixed before the path worked at all, each found by walking it rather than by reading it. (1) A DEADLOCK at the first save: a clinical trial saved before its milestones exist raises V-16 by definition, and its milestones cannot be entered until it is saved, because the milestone table hangs off a SELECTED project. The save guard now treats V-12 and V-16 as INCOMPLETENESS rather than error - the same line the specification already draws for drafts - names what is still missing in the banner, and refuses everything else exactly as before. (2) A row still being typed is not yet parsed into the model, so on a plan with no saved projects the Projects table said 'nothing matches the filters' and hid the very row the user was filling in. (3) The first assignment was the one row the application refused to name, having named every one after it: nextKey had nothing to copy a house style from, so the sheets that allocate their own keys now carry a pattern to start from. (4) FIVE PROJECT COLUMNS HAD NO HOME ANYWHERE IN THE APPLICATION. The project and people tables showed a curated subset, which was survivable while every plan arrived as a workbook filled in elsewhere; it is not survivable now that a plan can be built here, because DataReviewSystem_setup could never be entered and V-10 would warn about it forever. Both tables now carry every column the schema lets a user type into. Also: a person with no assignment yet is listed on the person tab, which is the state everybody is in for the minute after they are created; and the default horizon no longer anchors to year 0 when nothing has been calculated. tools/test_blank.py never touches a fixture - it clicks Start blank and builds a plan the way a person would, then checks every monthly figure against the formula worked by hand. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 19, application v1.18. The four CHILD sections are now on screen from the moment a blank plan is started, and can be filled in before their parent is saved. Round 18 made a plan enterable but only in one order: the project tab showed the Projects table alone until a project had been saved, and the person tab the People table alone. Both were literally true - the detail panels need a parent RECORD, with dates for the timeline and a name for every heading, and a row still being typed is not even parsed into the model - but the consequence was that Milestones, Periods, Assignments and Weight overrides were invisible to anyone building their first plan. A section that appears only after you have done something else reads as a section that does not exist. So the tables are drawn from the start, in the same two-column arrangement they have when a workbook is loaded, and they behave in three states. With no parent at all they are LOCKED and carry the reason where the '+ row' button would be, because a child row whose parent does not exist has nothing to attach to and would be dropped when the file is read back - saying so beats offering a button that creates a row nobody can rescue. The moment the parent row carries an IDENTIFIER - before it is saved - they unlock and scope themselves to it, so a plan can be entered the way a person actually thinks about one: the project and its milestones together, the person and their assignments together, each committed in a single Save. Two fixes were needed for that to work. The draft row now becomes the tab's selection, since child rows inherit their parent key from the selection and without it they were created parentless. And the fallback that finds the assignment for a new override row now reads the raw sheet rather than the validated array: the validated array excludes anything still being entered, so on a plan being typed from scratch the only assignment on screen was not found. tools/test_blank.py now enters the milestones BEFORE saving the project and the assignment BEFORE saving the person, checks each child inherited the right foreign key, and adds a weight override window to prove the fourth section works and REPLACES the person weight for its three months and no others. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.20</t>
+          <t>Superseded by v2.21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -8346,19 +8346,19 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 17, application v1.16. REFERENCE MATERIAL FOR ANOTHER AI SYSTEM, and an interoperability audit of everything delivered so far. The audit found one thing, and it was structural: of 95 files in the repository, 72 were .xlsx and 2 were Markdown. Every fact this project has established - the schema, the value lists, the formula, the twenty-four validation rules - existed only inside a ZIP of XML or inside the application's own JavaScript. A person with Excel could read all of it; a program, a script or a language model could read none of it. Four deliverables close that. (1) docs/prap_contract.json, a machine-readable contract carrying the schema, every column with its type and meaning, the value lists, the Config parameters, the formula term by term, the period derivation, all twenty-five rules with the severity the application actually reports, the interchange format and the task recipes. It is GENERATED - from the template builder, from this plan's own rule table, and from the application source - so it cannot drift from what it describes. (2) docs/PRAP_AI_Agent_Guide.md, the same contract written for a reader in the order an agent needs it, plus the same document as a workbook for human review. (3) A JSON INTERCHANGE FORMAT: the whole workbook as row objects keyed by column name, dates as yyyy-mm-dd. The application loads it and exports it, and tools/prap_io.py converts either way, so an agent that cannot write a ZIP of XML can still produce a file PRAP opens. (4) tools/prap_io.py also VALIDATES and CALCULATES from the command line, implementing the same rules and the same formula as the page - so an agent can check its own draft without a browser. tools/test_interop.py holds the two implementations to each other: same findings at the same severities, and every person-month equal to 1e-6, on both worked examples. The audit also found a rule the documents promised and the code did not keep: V-14 has been in the data model since v1.0 and the application never reported it. It does now - a milestone outside its project's window, or a boundary milestone out of order - with the one exception that is legitimate rather than merely noisy, an Inspection after the final DB lock, reported as information because the derivation deliberately extends the timeline to reach it. No requirement, calculation or schema version changed.</t>
+          <t>Gate 4 round 18, application v1.17. A PLAN CAN NOW BE STARTED IN THE APPLICATION ITSELF. The landing screen offers two ways in, given equal weight: load a source workbook, or start blank and type. 'Start blank' opens every tab and every section an upload opens - it is the same code path, so it is not a lesser mode with its own rules - and the plan it produces exports to the same .xlsx as any other. A blank start is not an EMPTY workbook: with no Lists sheet there would be no vocabulary, so every typed value would be reported as unrecognised (V-11) and no field could offer a choice, and with no Config there would be no thresholds. It therefore begins from the reference content of the delivered template, embedded in the HTML by tools/build_app_seed.py and held to the template by check_consistency.py. The PeriodFTEStandard and RoleFactor grids are NOT embedded: the application builds them from the value lists it was just seeded with - 56 standard weights and 289 role factors, every combination a project can reach - so a company that adds a role to Lists gets it without anybody regenerating anything. Every seeded figure is a placeholder 1.00 that says so on its own row, because an invented weight that looks like a company standard is worse than an obvious placeholder: only one of the two gets questioned. Four things had to be fixed before the path worked at all, each found by walking it rather than by reading it. (1) A DEADLOCK at the first save: a clinical trial saved before its milestones exist raises V-16 by definition, and its milestones cannot be entered until it is saved, because the milestone table hangs off a SELECTED project. The save guard now treats V-12 and V-16 as INCOMPLETENESS rather than error - the same line the specification already draws for drafts - names what is still missing in the banner, and refuses everything else exactly as before. (2) A row still being typed is not yet parsed into the model, so on a plan with no saved projects the Projects table said 'nothing matches the filters' and hid the very row the user was filling in. (3) The first assignment was the one row the application refused to name, having named every one after it: nextKey had nothing to copy a house style from, so the sheets that allocate their own keys now carry a pattern to start from. (4) FIVE PROJECT COLUMNS HAD NO HOME ANYWHERE IN THE APPLICATION. The project and people tables showed a curated subset, which was survivable while every plan arrived as a workbook filled in elsewhere; it is not survivable now that a plan can be built here, because DataReviewSystem_setup could never be entered and V-10 would warn about it forever. Both tables now carry every column the schema lets a user type into. Also: a person with no assignment yet is listed on the person tab, which is the state everybody is in for the minute after they are created; and the default horizon no longer anchors to year 0 when nothing has been calculated. tools/test_blank.py never touches a fixture - it clicks Start blank and builds a plan the way a person would, then checks every monthly figure against the formula worked by hand. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.19</t>
+          <t>Superseded by v2.20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -8378,19 +8378,19 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 16, application v1.15. A visual design pass over the whole interface, taking Apple's Human Interface Guidelines as the reference and applying them to a dense data tool. The stylesheet is rebuilt around TOKENS - one palette, one type scale, one radius scale, one motion curve - so that no value is chosen by eye at the point of use, which is what keeps a hundred small decisions consistent. Four changes carry most of the difference. (1) MATERIAL: white cards on a grey field, separated by soft shadow instead of by a 1px outline round every panel; dark mode inverts to lifted grey cards on near-black. (2) VIBRANCY: the two sticky bars are translucent and blurred, so content scrolling beneath stays legible as context - at an opacity that keeps their own labels readable over a chart, because blur alone is not enough when what is underneath is high-contrast. (3) The tab strip becomes a SEGMENTED CONTROL, and buttons take Apple's filled / tinted / plain hierarchy; the row actions that appear twice on every table row are furniture at rest and take colour only on hover, where blue means 'adds' and red means 'removes'. (4) COLOUR MEANS SOMETHING: blue is interactive, red is over the ceiling, amber is under the floor, everything else is a grey. Chart series colours are exempt, because there the colour IS the data, and they are unchanged. Contrast is now measured rather than judged: tools/test_contrast.py composites every text colour onto the surface it actually sits on and applies WCAG AA at the rendered size. The previous design had five colours below AA; this one has none. Two defects were found and fixed in passing: the drop zone still named template v1.6, and #editbar set display:flex from an id selector, which outranks the `hidden` attribute - so an empty edit bar showed before any workbook was loaded. No requirement, rule, calculation or schema changed, and every existing selector is retained.</t>
+          <t>Gate 4 round 17, application v1.16. REFERENCE MATERIAL FOR ANOTHER AI SYSTEM, and an interoperability audit of everything delivered so far. The audit found one thing, and it was structural: of 95 files in the repository, 72 were .xlsx and 2 were Markdown. Every fact this project has established - the schema, the value lists, the formula, the twenty-four validation rules - existed only inside a ZIP of XML or inside the application's own JavaScript. A person with Excel could read all of it; a program, a script or a language model could read none of it. Four deliverables close that. (1) docs/prap_contract.json, a machine-readable contract carrying the schema, every column with its type and meaning, the value lists, the Config parameters, the formula term by term, the period derivation, all twenty-five rules with the severity the application actually reports, the interchange format and the task recipes. It is GENERATED - from the template builder, from this plan's own rule table, and from the application source - so it cannot drift from what it describes. (2) docs/PRAP_AI_Agent_Guide.md, the same contract written for a reader in the order an agent needs it, plus the same document as a workbook for human review. (3) A JSON INTERCHANGE FORMAT: the whole workbook as row objects keyed by column name, dates as yyyy-mm-dd. The application loads it and exports it, and tools/prap_io.py converts either way, so an agent that cannot write a ZIP of XML can still produce a file PRAP opens. (4) tools/prap_io.py also VALIDATES and CALCULATES from the command line, implementing the same rules and the same formula as the page - so an agent can check its own draft without a browser. tools/test_interop.py holds the two implementations to each other: same findings at the same severities, and every person-month equal to 1e-6, on both worked examples. The audit also found a rule the documents promised and the code did not keep: V-14 has been in the data model since v1.0 and the application never reported it. It does now - a milestone outside its project's window, or a boundary milestone out of order - with the one exception that is legitimate rather than merely noisy, an Inspection after the final DB lock, reported as information because the derivation deliberately extends the timeline to reach it. No requirement, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.18</t>
+          <t>Superseded by v2.19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -8410,19 +8410,19 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 15, application v1.14, template v1.7, dummy v1.9 and 10x10 v1.1. DERIVED columns in the source workbook are now distinguished from entry columns by more than a colour: their cells are LOCKED, and the column heading carries a note saying what the column is, that the lock has no password, and what a hand-typed value would actually do. A green fill is a convention the reader must have been told about, and the telling is on a README sheet they may never open; a lock is the file itself refusing the edit at the moment it is attempted. Every other cell on those sheets is explicitly UNLOCKED, and protection is set so that inserting, deleting and sorting rows all still work - only adding or removing COLUMNS is blocked, because the column set is the schema. There is no password: it is a guard rail, not security, and anyone who genuinely needs to paste a column can turn it off in two clicks. The application's EXPORT now writes the same locks and the same sheet protection, so the guard rail survives a round trip instead of disappearing the first time a file goes through PRAP. check_consistency.py now verifies all of it against the plan's own data model - which surfaced a documentation gap the change had to close: Milestone.project_name and Assignment.person_name were typed 'Text' in the data model although the application recomputes both on import and reports any disagreement as V-13. They are typed 'Derived' now, which is what they have always been. No requirement, rule, calculation or schema version changed.</t>
+          <t>Gate 4 round 16, application v1.15. A visual design pass over the whole interface, taking Apple's Human Interface Guidelines as the reference and applying them to a dense data tool. The stylesheet is rebuilt around TOKENS - one palette, one type scale, one radius scale, one motion curve - so that no value is chosen by eye at the point of use, which is what keeps a hundred small decisions consistent. Four changes carry most of the difference. (1) MATERIAL: white cards on a grey field, separated by soft shadow instead of by a 1px outline round every panel; dark mode inverts to lifted grey cards on near-black. (2) VIBRANCY: the two sticky bars are translucent and blurred, so content scrolling beneath stays legible as context - at an opacity that keeps their own labels readable over a chart, because blur alone is not enough when what is underneath is high-contrast. (3) The tab strip becomes a SEGMENTED CONTROL, and buttons take Apple's filled / tinted / plain hierarchy; the row actions that appear twice on every table row are furniture at rest and take colour only on hover, where blue means 'adds' and red means 'removes'. (4) COLOUR MEANS SOMETHING: blue is interactive, red is over the ceiling, amber is under the floor, everything else is a grey. Chart series colours are exempt, because there the colour IS the data, and they are unchanged. Contrast is now measured rather than judged: tools/test_contrast.py composites every text colour onto the surface it actually sits on and applies WCAG AA at the rendered size. The previous design had five colours below AA; this one has none. Two defects were found and fixed in passing: the drop zone still named template v1.6, and #editbar set display:flex from an id selector, which outranks the `hidden` attribute - so an empty edit bar showed before any workbook was loaded. No requirement, rule, calculation or schema changed, and every existing selector is retained.</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.17</t>
+          <t>Superseded by v2.18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -8442,19 +8442,19 @@
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 14, application v1.13. (1) A LINE CHART of monthly resource now stands as the FIRST panel of every data tab - one coloured line per project on Overall and on the project tab, one per person on the person tab, each keeping the colour it already carries elsewhere. The stacked charts say what a month's total is MADE OF; they cannot say whether one series is rising or falling, because in a stack every band's baseline moves with the bands beneath it. Lines share one baseline, which is the whole reason to draw the same numbers a second way. Each line carries its total, mean and peak month, and is capped at the twelve largest by total because sixty lines on one axis is a texture, not a reading. On the person chart the over-allocation ceiling is marked, since there it applies to a single series' own value. (2) A design pass over every section. Summary tiles move to the TOP of the Overall tab: they are the headline figures and sat below a chart. Every panel now carries ONE header shape - title on the left, what the panel covers on the right - where scope had been stated three different ways: inside the caption, in a note under the table, or not at all, so the reader had to hunt for it in a different place in each section. Captions are bounded to a readable measure. Two long-standing chart faults were fixed on the way: a transparent stroke is not a PAINTED one, so the line hit strips needed pointer-events stated explicitly, and the visible stroke sits on top of them and had to be taken out of hit testing or it swallowed the pointer and offered no tip of its own. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 round 15, application v1.14, template v1.7, dummy v1.9 and 10x10 v1.1. DERIVED columns in the source workbook are now distinguished from entry columns by more than a colour: their cells are LOCKED, and the column heading carries a note saying what the column is, that the lock has no password, and what a hand-typed value would actually do. A green fill is a convention the reader must have been told about, and the telling is on a README sheet they may never open; a lock is the file itself refusing the edit at the moment it is attempted. Every other cell on those sheets is explicitly UNLOCKED, and protection is set so that inserting, deleting and sorting rows all still work - only adding or removing COLUMNS is blocked, because the column set is the schema. There is no password: it is a guard rail, not security, and anyone who genuinely needs to paste a column can turn it off in two clicks. The application's EXPORT now writes the same locks and the same sheet protection, so the guard rail survives a round trip instead of disappearing the first time a file goes through PRAP. check_consistency.py now verifies all of it against the plan's own data model - which surfaced a documentation gap the change had to close: Milestone.project_name and Assignment.person_name were typed 'Text' in the data model although the application recomputes both on import and reports any disagreement as V-13. They are typed 'Derived' now, which is what they have always been. No requirement, rule, calculation or schema version changed.</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.16</t>
+          <t>Superseded by v2.17</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -8474,19 +8474,19 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 13, application v1.12. PersonPeriodWeight is treated as what the schema says it is - a CHILD of Assignment - so on the person tab it now follows the assignment SELECTED above it, exactly as Milestones and Periods follow the project selected above them. Clicking a row in Assignments selects it and the overrides table redraws to that assignment's windows and no others; a new override row is seeded with the selected assignment rather than the person's first, so it is filed under the project on screen. Scoping the table to the PERSON instead - which is what round 12 left it doing - listed every window that person carries across every project at once, a set of rows with nothing to do with each other. Both headings now name the person ('Assignments - Kim S. (PSN-001)'), and the overrides panel restates the assignment it belongs to above the table: identifier, project, role, dates and weight. One structural change was needed to make this safe: the overrides panel is rendered into its own element, because clicking a cell both selects the row and puts the caret in it, and redrawing the whole person panel would rebuild the Assignments table under the caret so the edit could never be typed. The project and person tables escape this by living outside the panel they drive; this table drives a panel beside it. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 round 14, application v1.13. (1) A LINE CHART of monthly resource now stands as the FIRST panel of every data tab - one coloured line per project on Overall and on the project tab, one per person on the person tab, each keeping the colour it already carries elsewhere. The stacked charts say what a month's total is MADE OF; they cannot say whether one series is rising or falling, because in a stack every band's baseline moves with the bands beneath it. Lines share one baseline, which is the whole reason to draw the same numbers a second way. Each line carries its total, mean and peak month, and is capped at the twelve largest by total because sixty lines on one axis is a texture, not a reading. On the person chart the over-allocation ceiling is marked, since there it applies to a single series' own value. (2) A design pass over every section. Summary tiles move to the TOP of the Overall tab: they are the headline figures and sat below a chart. Every panel now carries ONE header shape - title on the left, what the panel covers on the right - where scope had been stated three different ways: inside the caption, in a note under the table, or not at all, so the reader had to hunt for it in a different place in each section. Captions are bounded to a readable measure. Two long-standing chart faults were fixed on the way: a transparent stroke is not a PAINTED one, so the line hit strips needed pointer-events stated explicitly, and the visible stroke sits on top of them and had to be taken out of hit testing or it swallowed the pointer and offered no tip of its own. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Issued for review</t>
+          <t>Superseded by v2.16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -8506,19 +8506,19 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 round 12, application v1.11. Three changes, none touching a requirement, rule, calculation or schema. (1) The Overall tab's 'Mean load per person' is replaced by 'MONTHLY DEMAND BY PERSON': the same months as 'Monthly demand by project' directly above it, cut the other way, one stacked band per person with a colour per person. The two charts total the same figure every month, because they are the same person-months summed along different axes - and that is now an executable check, not a claim. The mean-and-thresholds reading the old chart gave is not lost: a segment is OUTLINED where that person's own month crosses the ceiling or the floor, so the flag never rests on fill colour, which here already means 'which person' (D-04). The 20-person cap from D-14 carries over to the stack and its legend (REQ-DSH-09). (2) 'Utilisation' on the project tab is stacked by PERSON on the same terms, with each segment's pop-up naming the person, their role on this project, their FTE and share of the month, and the project's total. Its relative reference lines are unchanged, and a month whose TOTAL crosses one is outlined behind the stack rather than coloured into any one person's segment. (3) DEFECT: a row drafted on one person's tab appeared on every other person's tab. The child-table filters carried a bare '|| r.__new', added at round 6 so a new row would be visible before its key was filled in; being unconditional it admitted every draft everywhere. On 'Weight overrides', whose project and role columns are looked up FROM the assignment, such a row then described another person's work - the incorrect mapping reported. A draft is now admitted only while its parent key is empty, applied through one helper to all four child tables. The overrides table is also scoped correctly as a GRANDCHILD of the person: by the identifiers of the assignments shown above it, not by the person's own.</t>
+          <t>Gate 4 round 13, application v1.12. PersonPeriodWeight is treated as what the schema says it is - a CHILD of Assignment - so on the person tab it now follows the assignment SELECTED above it, exactly as Milestones and Periods follow the project selected above them. Clicking a row in Assignments selects it and the overrides table redraws to that assignment's windows and no others; a new override row is seeded with the selected assignment rather than the person's first, so it is filed under the project on screen. Scoping the table to the PERSON instead - which is what round 12 left it doing - listed every window that person carries across every project at once, a set of rows with nothing to do with each other. Both headings now name the person ('Assignments - Kim S. (PSN-001)'), and the overrides panel restates the assignment it belongs to above the table: identifier, project, role, dates and weight. One structural change was needed to make this safe: the overrides panel is rendered into its own element, because clicking a cell both selects the row and puts the caret in it, and redrawing the whole person panel would rebuild the Assignments table under the caret so the edit could never be typed. The project and person tables escape this by living outside the panel they drive; this table drives a panel beside it. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.14</t>
+          <t>Issued for review</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -8538,19 +8538,19 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 11, application v1.10. Two changes, neither touching a requirement, rule, calculation or schema. (1) A PROJECT TIMELINE run-chart now stands before the Utilisation panel on the project tab - the Overall tab's chart drawn for the selected project alone, with one band per period shaded by period weight, every milestone marked, the two DB locks in red, and each band labelled with its average FTE per month. The row-label gutter the Overall chart needs is dropped, since the panel heading already names the project. (2) The UTILISATION bars on the person tab are now STACKED BY PROJECT: one coloured segment per project per month. The total says whether someone is over the ceiling; only the split says because of what. Each segment's pop-up answers both halves at once - the project (name, type, the milestones that project passes THAT month, this person's FTE on it and its share of the month) and the person (name, identifier, total FTE that month, how many projects it is spread across, capacity, and which threshold if any it crosses). Over- and under-allocation is now drawn as an outline BEHIND the stack, because it is a property of the month's total and not of any one project in it. Supporting this, project colours are now allocated from the sorted list of ALL project ids and held for the session, so one project carries ONE colour everywhere - the Overall stacked chart picked its colours from the filtered draw order, which meant the same colour meant different projects on different tabs and after every filter change.</t>
+          <t>Gate 4 round 12, application v1.11. Three changes, none touching a requirement, rule, calculation or schema. (1) The Overall tab's 'Mean load per person' is replaced by 'MONTHLY DEMAND BY PERSON': the same months as 'Monthly demand by project' directly above it, cut the other way, one stacked band per person with a colour per person. The two charts total the same figure every month, because they are the same person-months summed along different axes - and that is now an executable check, not a claim. The mean-and-thresholds reading the old chart gave is not lost: a segment is OUTLINED where that person's own month crosses the ceiling or the floor, so the flag never rests on fill colour, which here already means 'which person' (D-04). The 20-person cap from D-14 carries over to the stack and its legend (REQ-DSH-09). (2) 'Utilisation' on the project tab is stacked by PERSON on the same terms, with each segment's pop-up naming the person, their role on this project, their FTE and share of the month, and the project's total. Its relative reference lines are unchanged, and a month whose TOTAL crosses one is outlined behind the stack rather than coloured into any one person's segment. (3) DEFECT: a row drafted on one person's tab appeared on every other person's tab. The child-table filters carried a bare '|| r.__new', added at round 6 so a new row would be visible before its key was filled in; being unconditional it admitted every draft everywhere. On 'Weight overrides', whose project and role columns are looked up FROM the assignment, such a row then described another person's work - the incorrect mapping reported. A draft is now admitted only while its parent key is empty, applied through one helper to all four child tables. The overrides table is also scoped correctly as a GRANDCHILD of the person: by the identifiers of the assignments shown above it, not by the person's own.</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.13</t>
+          <t>Superseded by v2.14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -8570,19 +8570,19 @@
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 defect fix round 10, application v1.9. Reviewer reported that dragging the scroll bar of a type-ahead value list closed the list, making a list taller than its box impossible to read to the bottom of. Two independent causes, both now fixed. (1) A capturing scroll listener closed the list on ANY scroll anywhere in the document - including the list's OWN scrolling. It existed because the list is a fixed box anchored to its cell and a page scroll would leave it stranded; closing was the crude answer. It now ignores its own scrolling and RE-ANCHORS on any other, closing only once the cell itself has left the screen. (2) Pressing on the list's scroll bar took focus off the cell, and the focus-out handler closed the list underneath the hand scrolling it. The press is now held for its whole duration and the caret is restored on release. The list closes on exactly the three things asked for: choosing a value, Escape, or a click outside. Because Escape leaves the caret in the cell and so fires no focus event, a click in the field now re-opens the list. Matching is also improved: tokens match in ANY ORDER, so 'phase 1 onv' finds 'ONV-101 Phase 1'; every matched fragment is marked, not just the first; results rank a typed prefix above a mere containment; and a query matching nothing now shows the whole vocabulary with an explanation instead of vanishing and stranding the reader. That last change exposed a pre-existing trap - render() highlighted the first row, so Enter silently swapped in a value the user never chose, which had escaped notice only because a query matching nothing used to hide the list and put Enter out of its reach. Nothing is highlighted now until an arrow key highlights it. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 refinements round 11, application v1.10. Two changes, neither touching a requirement, rule, calculation or schema. (1) A PROJECT TIMELINE run-chart now stands before the Utilisation panel on the project tab - the Overall tab's chart drawn for the selected project alone, with one band per period shaded by period weight, every milestone marked, the two DB locks in red, and each band labelled with its average FTE per month. The row-label gutter the Overall chart needs is dropped, since the panel heading already names the project. (2) The UTILISATION bars on the person tab are now STACKED BY PROJECT: one coloured segment per project per month. The total says whether someone is over the ceiling; only the split says because of what. Each segment's pop-up answers both halves at once - the project (name, type, the milestones that project passes THAT month, this person's FTE on it and its share of the month) and the person (name, identifier, total FTE that month, how many projects it is spread across, capacity, and which threshold if any it crosses). Over- and under-allocation is now drawn as an outline BEHIND the stack, because it is a property of the month's total and not of any one project in it. Supporting this, project colours are now allocated from the sorted list of ALL project ids and held for the session, so one project carries ONE colour everywhere - the Overall stacked chart picked its colours from the filtered draw order, which meant the same colour meant different projects on different tabs and after every filter change.</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Issued for review</t>
+          <t>Superseded by v2.13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -8602,19 +8602,19 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 defect fix round 9, application v1.8. Reviewer reported that choosing an assignment_id on a new Weight-overrides row raised a warning offering to change every other override of the assignment being moved away from, so a second window could not be added. Cause: the edit path cascaded an identifier change whenever the edited column was the sheet's KEY_COL, but on a CHILD sheet that column is a FOREIGN key - PersonPeriodWeight.assignment_id points at an assignment, it does not define one. Re-pointing one row therefore rewrote every row sharing the old value, which on the overrides table is the sibling windows of that same assignment. Accepting the prompt destroyed them; declining abandoned the edit, so the assignment could not be changed at all and the row stayed on whichever assignment it was seeded with. The cascade is now confined to the sheet that OWNS the identifier, using the OWNER map that deleteRow has used for the same distinction since round 4. In place of the warning, picking an assignment that already carries windows now states how many the row joins and names V-06 and V-24 - an additional window is the normal case, and only an overlapping one is refused, at Save. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 defect fix round 10, application v1.9. Reviewer reported that dragging the scroll bar of a type-ahead value list closed the list, making a list taller than its box impossible to read to the bottom of. Two independent causes, both now fixed. (1) A capturing scroll listener closed the list on ANY scroll anywhere in the document - including the list's OWN scrolling. It existed because the list is a fixed box anchored to its cell and a page scroll would leave it stranded; closing was the crude answer. It now ignores its own scrolling and RE-ANCHORS on any other, closing only once the cell itself has left the screen. (2) Pressing on the list's scroll bar took focus off the cell, and the focus-out handler closed the list underneath the hand scrolling it. The press is now held for its whole duration and the caret is restored on release. The list closes on exactly the three things asked for: choosing a value, Escape, or a click outside. Because Escape leaves the caret in the cell and so fires no focus event, a click in the field now re-opens the list. Matching is also improved: tokens match in ANY ORDER, so 'phase 1 onv' finds 'ONV-101 Phase 1'; every matched fragment is marked, not just the first; results rank a typed prefix above a mere containment; and a query matching nothing now shows the whole vocabulary with an explanation instead of vanishing and stranding the reader. That last change exposed a pre-existing trap - render() highlighted the first row, so Enter silently swapped in a value the user never chose, which had escaped notice only because a query matching nothing used to hide the list and put Enter out of its reach. Nothing is highlighted now until an arrow key highlights it. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.11</t>
+          <t>Issued for review</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -8634,19 +8634,19 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 8, application v1.7. Three changes, none touching a requirement, rule, calculation or schema. (1) EVERY scroll region now scrolls in BOTH directions and is bounded on both axes. A panel bounded on one axis only can still hide content on the other, and the reader has no way of telling that it has - there is no scrollbar to suggest anything is missing. The findings dialog and the provenance strip were the two regions with no bound at all; the three chart panels were bounded sideways only. (2) On the Assignments table the project is now identified by NAME: project_name is the field typed into and project_id is derived from it, with a type-ahead over the project names. Editing the identifier directly still works and the name follows instead - the two are one field seen from two ends. A name matching no project is refused, naming near matches; an ambiguous one is refused too, since only the identifier is guaranteed unique. The name is never STORED on the assignment row: the sheet has no such column, so a copy could not survive an export and re-import, and it would be a second version of a fact the Project sheet already owns. (3) '+ row' on the Assignments table allocates the next free assignment_id - the smallest unused number in the pattern the file already uses, not the largest plus one, so a file whose ids jump to 901 for a few hand-placed rows does not start allocating 905.</t>
+          <t>Gate 4 defect fix round 9, application v1.8. Reviewer reported that choosing an assignment_id on a new Weight-overrides row raised a warning offering to change every other override of the assignment being moved away from, so a second window could not be added. Cause: the edit path cascaded an identifier change whenever the edited column was the sheet's KEY_COL, but on a CHILD sheet that column is a FOREIGN key - PersonPeriodWeight.assignment_id points at an assignment, it does not define one. Re-pointing one row therefore rewrote every row sharing the old value, which on the overrides table is the sibling windows of that same assignment. Accepting the prompt destroyed them; declining abandoned the edit, so the assignment could not be changed at all and the row stayed on whichever assignment it was seeded with. The cascade is now confined to the sheet that OWNS the identifier, using the OWNER map that deleteRow has used for the same distinction since round 4. In place of the warning, picking an assignment that already carries windows now states how many the row joins and names V-06 and V-24 - an additional window is the normal case, and only an overlapping one is refused, at Save. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.10</t>
+          <t>Superseded by v2.11</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -8666,19 +8666,19 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 round 7, application unchanged at v1.6. A second dummy dataset at the reviewer's requested size - 10 projects and 10 people - issued as PRAP_SourceData_Dummy_10x10_v1.0.xlsx on schema 5, alongside the 62-project set rather than replacing it. The generator now runs from size PROFILES, so one code path produces both and neither can drift from the schema the other follows; the 62-project file rebuilds with every sheet byte-identical, confirmed by unpacking both .xlsx containers. The small set is not a lighter test: it holds both clinical types, all four phases, trials with and without an interim DB lock, inspections that open the seventh period, hand-entered 'Others' periods, two part-timers, multi-window weight overrides, and both allocation thresholds crossed. Its load distribution matches the large set's (median 0.80 against 0.87 FTE). tools/test_app.py now runs over BOTH fixtures. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 refinements round 8, application v1.7. Three changes, none touching a requirement, rule, calculation or schema. (1) EVERY scroll region now scrolls in BOTH directions and is bounded on both axes. A panel bounded on one axis only can still hide content on the other, and the reader has no way of telling that it has - there is no scrollbar to suggest anything is missing. The findings dialog and the provenance strip were the two regions with no bound at all; the three chart panels were bounded sideways only. (2) On the Assignments table the project is now identified by NAME: project_name is the field typed into and project_id is derived from it, with a type-ahead over the project names. Editing the identifier directly still works and the name follows instead - the two are one field seen from two ends. A name matching no project is refused, naming near matches; an ambiguous one is refused too, since only the identifier is guaranteed unique. The name is never STORED on the assignment row: the sheet has no such column, so a copy could not survive an export and re-import, and it would be a second version of a fact the Project sheet already owns. (3) '+ row' on the Assignments table allocates the next free assignment_id - the smallest unused number in the pattern the file already uses, not the largest plus one, so a file whose ids jump to 901 for a few hand-placed rows does not start allocating 905.</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.9</t>
+          <t>Superseded by v2.10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -8698,19 +8698,19 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 defect fix round 6, application v1.6. Reviewer reported that inserting and deleting rows did not work on Milestones, Periods, Assignments and Weight overrides - the four CHILD tables, which are the four rendered filtered to a selected parent. Three defects, all in the shared insert/rebuild path, none touching a requirement, rule, calculation or schema. (D-1) A new row was created with every column empty, so the parent filter that decides which rows the table shows excluded it: the row existed but was invisible. A new child row is now seeded with the parent it was created under, and each filter admits a row still being drafted. (D-2) Every edit and delete re-parses the data, and the parser discards blank rows - correct for a file being read, wrong for a row the user has not filled in yet, which was silently destroyed by the next action. Rows the parser would discard are now held out of the parse and put back in place. (D-3) The parser numbers rows by position, so deleting a row renumbered every row below it while pending edits, edit highlights and the rendered cells still named the old numbers - an edit could end up attached to a different record, and a drafted row could be duplicated. Row identity is now preserved across a rebuild. A drafted row is exempt from validation while it is being written and is validated when Save is pressed; a draft that would break a rule is refused by name rather than kept.</t>
+          <t>Gate 4 round 7, application unchanged at v1.6. A second dummy dataset at the reviewer's requested size - 10 projects and 10 people - issued as PRAP_SourceData_Dummy_10x10_v1.0.xlsx on schema 5, alongside the 62-project set rather than replacing it. The generator now runs from size PROFILES, so one code path produces both and neither can drift from the schema the other follows; the 62-project file rebuilds with every sheet byte-identical, confirmed by unpacking both .xlsx containers. The small set is not a lighter test: it holds both clinical types, all four phases, trials with and without an interim DB lock, inspections that open the seventh period, hand-entered 'Others' periods, two part-timers, multi-window weight overrides, and both allocation thresholds crossed. Its load distribution matches the large set's (median 0.80 against 0.87 FTE). tools/test_app.py now runs over BOTH fixtures. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v2.8</t>
+          <t>Superseded by v2.9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -8730,19 +8730,19 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 5, application v1.5. Five changes, none touching a requirement, rule, calculation or schema. (1) and (2) The Assignments and Weight-overrides tables carry the project name, and the overrides table also the role - looked up from the master row and marked as such, since an identifier alone does not tell a reader which project they are looking at. (3) Every data cell shows its value and its column's meaning on hover or focus. (4) The Periods table and the General-assumptions tables gain row actions. The two weight sheets and the value lists keep their matrix view for reading and gain a rows view for editing, because a matrix row is six or seven workbook rows and cannot carry a per-row action. (5) Type-ahead on every column with a vocabulary: the Lists sheet where the column is backed by one, the distinct values already present where it is not, and the type-dependent set for period_name and role_name.</t>
+          <t>Gate 4 defect fix round 6, application v1.6. Reviewer reported that inserting and deleting rows did not work on Milestones, Periods, Assignments and Weight overrides - the four CHILD tables, which are the four rendered filtered to a selected parent. Three defects, all in the shared insert/rebuild path, none touching a requirement, rule, calculation or schema. (D-1) A new row was created with every column empty, so the parent filter that decides which rows the table shows excluded it: the row existed but was invisible. A new child row is now seeded with the parent it was created under, and each filter admits a row still being drafted. (D-2) Every edit and delete re-parses the data, and the parser discards blank rows - correct for a file being read, wrong for a row the user has not filled in yet, which was silently destroyed by the next action. Rows the parser would discard are now held out of the parse and put back in place. (D-3) The parser numbers rows by position, so deleting a row renumbered every row below it while pending edits, edit highlights and the rendered cells still named the old numbers - an edit could end up attached to a different record, and a drafted row could be duplicated. Row identity is now preserved across a rebuild. A drafted row is exempt from validation while it is being written and is validated when Save is pressed; a draft that would break a rule is refused by name rather than kept.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v2.7</t>
+          <t>Superseded by v2.8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -8762,19 +8762,19 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 4, application v1.4. (1) Information pop-ups: every column heading on the source-data tabs explains what its column is for, and the summary tiles, month headings and project type pills explain what they count. They open on HOVER and PIN on CLICK, which is also what makes them reachable on a touch screen and from the keyboard, where there is no hover at all. (2) Every editable table gains a Delete control beside Insert. V-17 governs it: a row still referenced cannot be deleted and the refusal names what refers to it, and a delete is NEVER cascaded - that asymmetry with the cascading identifier edit is deliberate, because a cascaded rename is reversible and a cascaded delete is not. Deletion is provisional like any other change. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 refinements round 5, application v1.5. Five changes, none touching a requirement, rule, calculation or schema. (1) and (2) The Assignments and Weight-overrides tables carry the project name, and the overrides table also the role - looked up from the master row and marked as such, since an identifier alone does not tell a reader which project they are looking at. (3) Every data cell shows its value and its column's meaning on hover or focus. (4) The Periods table and the General-assumptions tables gain row actions. The two weight sheets and the value lists keep their matrix view for reading and gain a rows view for editing, because a matrix row is six or seven workbook rows and cannot carry a per-row action. (5) Type-ahead on every column with a vocabulary: the Lists sheet where the column is backed by one, the distinct values already present where it is not, and the type-dependent set for period_name and role_name.</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>Issued for review</t>
+          <t>Superseded by v2.7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 3, application v1.3. Three changes. (1) Column headings stay visible in EVERY scroll region, and the corner cell of the two Overall grids is pinned in both directions - a month heading that scrolls away turns the table into unlabelled numbers. (2) The two utilisation charts carry the year on the x axis, shown where the year changes with a divider at each boundary. (3) EDITING IS NOW PROVISIONAL: a change is applied on screen so its effect is visible, but is held as pending until the user presses Save or Leave without change. Save commits it to the working data; Leave without change restores the snapshot taken before the first pending edit. Export is HELD while anything is pending, so nothing unconfirmed can reach a file. This is a behavioural change to REQ-IMP-07 and REQ-IMP-08 and is recorded for the specification to take up at the next issue.</t>
+          <t>Gate 4 refinements round 4, application v1.4. (1) Information pop-ups: every column heading on the source-data tabs explains what its column is for, and the summary tiles, month headings and project type pills explain what they count. They open on HOVER and PIN on CLICK, which is also what makes them reachable on a touch screen and from the keyboard, where there is no hover at all. (2) Every editable table gains a Delete control beside Insert. V-17 governs it: a row still referenced cannot be deleted and the refusal names what refers to it, and a delete is NEVER cascaded - that asymmetry with the cascading identifier edit is deliberate, because a cascaded rename is reversible and a cascaded delete is not. Deletion is provisional like any other change. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -8806,7 +8806,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Gate 4 refinements round 2, application v1.2. The application now shows, at the top of the page, which controlled documents the build implements - development plan, programming specification, UI component list and source-data template - collapsed to one line with the full table on demand, and a row comparing the loaded workbook's schema version against the one the application expects. This is REQ-VC-01 made visible in the product rather than only in the repository. The list is data in one place and is verified against the repository by tools/check_consistency.py on every run, which was proved to fire by naming a superseded plan version. No requirement, rule, calculation or schema changed.</t>
+          <t>Gate 4 refinements round 3, application v1.3. Three changes. (1) Column headings stay visible in EVERY scroll region, and the corner cell of the two Overall grids is pinned in both directions - a month heading that scrolls away turns the table into unlabelled numbers. (2) The two utilisation charts carry the year on the x axis, shown where the year changes with a divider at each boundary. (3) EDITING IS NOW PROVISIONAL: a change is applied on screen so its effect is visible, but is held as pending until the user presses Save or Leave without change. Save commits it to the working data; Leave without change restores the snapshot taken before the first pending edit. Export is HELD while anything is pending, so nothing unconfirmed can reach a file. This is a behavioural change to REQ-IMP-07 and REQ-IMP-08 and is recorded for the specification to take up at the next issue.</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -8838,7 +8838,7 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>First refinements from the Gate 4 review (WBS 4.9), applied to application v1.1. Three UI changes, no change to any requirement, rule, calculation or schema. (1) The three named Overall sections - monthly demand, resource by project, resource by person - are up to twice their previous size. (2) The project timeline scrolls in both directions inside its panel, which also let the 20-project display cap be removed: every project in the filter is now drawn. (3) Chart text is larger and higher contrast, and each threshold or reference label moved out of the plot area into a right-hand margin - drawn over the bars they were unreadable at any size, and enlarging them made the collision worse rather than better. Breaching bars on the person chart now state their own value.</t>
+          <t>Gate 4 refinements round 2, application v1.2. The application now shows, at the top of the page, which controlled documents the build implements - development plan, programming specification, UI component list and source-data template - collapsed to one line with the full table on demand, and a row comparing the loaded workbook's schema version against the one the application expects. This is REQ-VC-01 made visible in the product rather than only in the repository. The list is data in one place and is verified against the repository by tools/check_consistency.py on every run, which was proved to fire by naming a superseded plan version. No requirement, rule, calculation or schema changed.</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -8870,7 +8870,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Step 4 progress against the v2.0 baseline. The application is built: app/PRAP.html, one offline file with its own .xlsx reader and writer. WBS tasks 4.1 to 4.8 move to Complete; 4.9 - your review of the output against real data - is the Gate 4 review and is what remains. No requirement, rule or schema changed: this issue records progress, not a change of intent. The calculation engine was checked cell-by-cell against tools/verify_source_workbook.py and matches exactly across all 1,225 person-months of the dummy dataset.</t>
+          <t>First refinements from the Gate 4 review (WBS 4.9), applied to application v1.1. Three UI changes, no change to any requirement, rule, calculation or schema. (1) The three named Overall sections - monthly demand, resource by project, resource by person - are up to twice their previous size. (2) The project timeline scrolls in both directions inside its panel, which also let the 20-project display cap be removed: every project in the filter is now drawn. (3) Chart text is larger and higher contrast, and each threshold or reference label moved out of the plot area into a right-hand margin - drawn over the bars they were unreadable at any size, and enlarging them made the collision worse rather than better. Breaching bars on the person chart now state their own value.</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -8902,12 +8902,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -8917,29 +8917,29 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>APPROVED BASELINE. Content identical to v1.10; the version number changes because the numbering rule on sheet 09 reserves x.0 for an approved baseline and v1.10 was a change awaiting signature. Approved together with programming specification v1.0 and UI component list v1.0. Changes R-05 to R-13 are now part of the baseline rather than pending against v1.3, and Step 4 is authorised.</t>
+          <t>Step 4 progress against the v2.0 baseline. The application is built: app/PRAP.html, one offline file with its own .xlsx reader and writer. WBS tasks 4.1 to 4.8 move to Complete; 4.9 - your review of the output against real data - is the Gate 4 review and is what remains. No requirement, rule or schema changed: this issue records progress, not a change of intent. The calculation engine was checked cell-by-cell against tools/verify_source_workbook.py and matches exactly across all 1,225 person-months of the dummy dataset.</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>APPROVED 2026-08-02 by Dan - BASELINE</t>
+          <t>Issued for review</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -8949,24 +8949,24 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Change R-13, from the component-list v0.7 review. All 13 changed components and all 7 changed decisions were confirmed OK; nothing was marked Rework. Two new requests were raised and both are applied: the interim and final DB lock milestones are emphasised on the timeline, and the project source-data tab gains a utilisation graph. The second needed a new requirement, REQ-DSH-12, because a project has no absolute ceiling or floor - its reference lines are relative to the portfolio average and to the project's own lifetime average. No schema change.</t>
+          <t>APPROVED BASELINE. Content identical to v1.10; the version number changes because the numbering rule on sheet 09 reserves x.0 for an approved baseline and v1.10 was a change awaiting signature. Approved together with programming specification v1.0 and UI component list v1.0. Changes R-05 to R-13 are now part of the baseline rather than pending against v1.3, and Step 4 is authorised.</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>Issued for approval</t>
+          <t>APPROVED 2026-08-02 by Dan - BASELINE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Change R-12. A reviewer question about the PersonPeriodWeight key - why period_start is needed when assignment_id looks unique - was answered by confirming the key is correct: one assignment may carry several non-overlapping override windows, so assignment_id alone would cap it at one. Checking the question found two rules that were specified but never implemented. V-06's assignment-window half now runs, and V-24 is added for referential integrity and key uniqueness on PersonPeriodWeight. The dummy fixture gains an assignment with two windows, which is what would have caught both. No schema change.</t>
+          <t>Change R-13, from the component-list v0.7 review. All 13 changed components and all 7 changed decisions were confirmed OK; nothing was marked Rework. Two new requests were raised and both are applied: the interim and final DB lock milestones are emphasised on the timeline, and the project source-data tab gains a utilisation graph. The second needed a new requirement, REQ-DSH-12, because a project has no absolute ceiling or floor - its reference lines are relative to the portfolio average and to the project's own lifetime average. No schema change.</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -8998,7 +8998,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -9018,19 +9018,19 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Change R-11 against the v1.3 baseline. The conduct phase is split by NAME rather than by sequence: 'Conduct (interim)' where an interim DB lock exists and the stretch runs before it, 'Conduct (final)' after it or where there is no interim lock. Period names are therefore unique within a project and ProjectPeriod is keyed on (project_id, period_name); period_seq carries order only. The clinical period set grows to seven names, V-18 becomes a uniqueness check, REQ-CAL-11 and REQ-PRJ-12 are reworded, and REQ-DSH-10 is now satisfied structurally rather than by display numbering. Schema version steps 4 to 5. Weights are unchanged, so the dummy dataset produces identical figures.</t>
+          <t>Change R-12. A reviewer question about the PersonPeriodWeight key - why period_start is needed when assignment_id looks unique - was answered by confirming the key is correct: one assignment may carry several non-overlapping override windows, so assignment_id alone would cap it at one. Checking the question found two rules that were specified but never implemented. V-06's assignment-window half now runs, and V-24 is added for referential integrity and key uniqueness on PersonPeriodWeight. The dummy fixture gains an assignment with two windows, which is what would have caught both. No schema change.</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>Superseded by v1.9</t>
+          <t>Issued for approval</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
@@ -9050,49 +9050,81 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Change R-10 against the v1.3 baseline, from the component-list v0.4 review. The role factor is now keyed on project type, clinical phase, period and role rather than type and role alone, so a role's burden can vary across the life of a project. RoleFactor gains clinical_phase and period_name and grows from 13 rows to 249; REQ-CAL-02 reworded; V-23 added for a factor missing on a period an assignment actually spans; source schema version steps 3 to 4. A consequence is recorded on sheet 04: RoleFactor and PeriodWeightStandard now vary over the same three dimensions and multiply together, so they must not both be edited for the same reason.</t>
+          <t>Change R-11 against the v1.3 baseline. The conduct phase is split by NAME rather than by sequence: 'Conduct (interim)' where an interim DB lock exists and the stretch runs before it, 'Conduct (final)' after it or where there is no interim lock. Period names are therefore unique within a project and ProjectPeriod is keyed on (project_id, period_name); period_seq carries order only. The clinical period set grows to seven names, V-18 becomes a uniqueness check, REQ-CAL-11 and REQ-PRJ-12 are reworded, and REQ-DSH-10 is now satisfied structurally rather than by display numbering. Schema version steps 4 to 5. Weights are unchanged, so the dummy dataset produces identical figures.</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Superseded by v1.8</t>
+          <t>Superseded by v1.9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>Change R-10 against the v1.3 baseline, from the component-list v0.4 review. The role factor is now keyed on project type, clinical phase, period and role rather than type and role alone, so a role's burden can vary across the life of a project. RoleFactor gains clinical_phase and period_name and grows from 13 rows to 249; REQ-CAL-02 reworded; V-23 added for a factor missing on a period an assignment actually spans; source schema version steps 3 to 4. A consequence is recorded on sheet 04: RoleFactor and PeriodWeightStandard now vary over the same three dimensions and multiply together, so they must not both be edited for the same reason.</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Superseded by v1.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Claude Code</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E74" s="11" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>Change R-09 against the v1.3 baseline, from the component-list v0.3 review. Nine components changed; two needed requirements the plan did not have. REQ-DSH-11 added - the standing assumptions get their own tab. REQ-IMP-11 added - a row can be inserted, positioned below the row acted on. REQ-DSH-05 reworded for the clinical-phase filter and to stop implying the display unit is a filter; REQ-IMP-05 reworded for the time zone. Sheet 06 now describes four tabs. Design decision D-06 is superseded by the reviewer's own O-10, which asks for the opposite. Version history rows for v1.4 and v1.5 added above - they were issued without one, which REQ-VC-04 requires.</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>Issued for approval</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>The reviewer's file was named v0.11. Under the numbering rule on sheet 09 that reads as a draft increment of v0.1, so it is logged above as review input and this incorporating draft is v0.2.</t>
         </is>
@@ -10606,7 +10638,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>WHERE A FIGURE'S SIZE WAS DECIDED SOMEWHERE ELSE, THE TABLE SHOWING THE FIGURE NAMES WHAT DECIDED IT, in a column that is looked up and cannot be edited. Three of them, because three tables each showed one term of an expression and left the reader to find the rest in another tab: the Periods table names the STANDARD MONTHLY FTE its period selects and multiplies it by the project's own weight, so the row carries the month's demand instead of half the expression for it; both Monthly estimation panels name the PERIOD the month falls in and the weight that period carried; and the person's panel also names HOW MANY PEOPLE held that role that month, which is the divisor in (role factor / sharers) and the usual explanation for a share that halved with nothing of the person's own changing. LOOKED UP, NEVER STORED: none of the three is a column of the sheet it is shown beside, so no edit and no save can leave a stale copy of a standard in a file after the standards have moved - which is the failure the lookup exists to prevent. NAMED FROM THE CALCULATION'S OWN WORKINGS, not by asking the sheets again, so a screen cannot name one period while the figure beside it came from another. A missing standard says it is missing and names V-19 rather than printing the 1.00 the calculation falls back to; that fallback is a degradation, and showing it as a standard would hide the very thing V-19 reports.</t>
+          <t>WHERE A FIGURE'S SIZE WAS DECIDED SOMEWHERE ELSE, THE TABLE SHOWING THE FIGURE NAMES WHAT DECIDED IT, in a column that is looked up and cannot be edited. Three of them, because three tables each showed one term of an expression and left the reader to find the rest in another tab: the Periods table names the STANDARD MONTHLY FTE its period selects and multiplies it by the project's own weight, so the row carries the month's demand instead of half the expression for it; both Monthly estimation panels carry THE WHOLE DERIVATION OF THE MONTH, TERM BY TERM - the period it falls in, the standard that period selects, the project's own weight, how much of the month it ran, and their product - so a reader who disagrees with an automatic figure can see WHICH of the inputs they disagree with rather than only that they disagree. The person's panel adds their CLAIM on that month: role factor / sharers x person weight x month coverage, ending in the PERCENTAGE of the project's month it won. The two halves are closed off SEPARATELY and the person's is stated as a proportion, never as a product equal to the figure, because since R-32 it is not one - the claim is normalised against every other claim on that project-month (REQ-CAL-19), so terms multiplying to 0.60 can give a figure of 2.40, and writing them as one product would assert an arithmetic the application does not do. A PersonPeriodWeight override is shown as ONE TERM WITH TWO SOURCES rather than as a second factor: it REPLACES person_weight for the months it covers (REQ-PSN-05), and the cell names both values and says which was used. The sharer count also keeps a short column of its own, where it can be sorted and filtered - the derivation is a sentence and is neither. Every fallback SAYS it is a fallback and names its rule - V-19 for a missing standard, V-23 for a missing role factor, V-12 for a month in no period - because a bare 1.00 is indistinguishable from a standard that really is 1.00, which is the whole reason those rules exist. LOOKED UP, NEVER STORED: none of the three is a column of the sheet it is shown beside, so no edit and no save can leave a stale copy of a standard in a file after the standards have moved - which is the failure the lookup exists to prevent. NAMED FROM THE CALCULATION'S OWN WORKINGS, not by asking the sheets again, so a screen cannot name one period while the figure beside it came from another. A missing standard says it is missing and names V-19 rather than printing the 1.00 the calculation falls back to; that fallback is a degradation, and showing it as a standard would hide the very thing V-19 reports.</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
